--- a/youzi/金田路/index.xlsx
+++ b/youzi/金田路/index.xlsx
@@ -45,6 +45,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -57,79 +111,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,55 +171,811 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE15361"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C78A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA2AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77882"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBC73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2AA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4DB665"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF24993F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15361"/>
+        <fgColor rgb="FFE9F6EC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,25 +987,379 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -231,1152 +1371,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77882"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA2AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBC73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2AA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4DB665"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -1396,6 +1390,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4121,40 +4121,40 @@
       <c r="H2">
         <v>526.19</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="11">
         <v>12.88</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="7">
         <v>-12.55</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="2">
         <v>-22.7</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="3">
         <v>-26.47</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="8">
         <v>-25.17</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="4">
         <v>-30.67</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="9">
         <v>-32.55</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="10">
         <v>-31.88</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="5">
         <v>-29.12</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="6">
         <v>-30.52</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="12">
         <v>-28.5</v>
       </c>
-      <c r="T2" s="11">
+      <c r="T2" s="13">
         <v>87.91</v>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       <c r="C3" t="str">
         <v>605298</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="17" t="str">
         <v>净卖: -183.82万</v>
       </c>
       <c r="E3">
@@ -4183,37 +4183,37 @@
       <c r="H3">
         <v>-4.14</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="24">
         <v>-6.15</v>
       </c>
       <c r="J3" s="20">
         <v>-1.99</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="25">
         <v>-0.75</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="26">
         <v>3.41</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="19">
         <v>7.06</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="21">
         <v>9.39</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="22">
         <v>5.32</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="23">
         <v>4.24</v>
       </c>
       <c r="Q3" s="14">
         <v>4.98</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="15">
         <v>6.56</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="16">
         <v>4.73</v>
       </c>
       <c r="T3" s="18">
@@ -4230,7 +4230,7 @@
       <c r="C4" t="str">
         <v>600418</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="30" t="str">
         <v>净卖: -8419.55万</v>
       </c>
       <c r="E4">
@@ -4245,40 +4245,40 @@
       <c r="H4">
         <v>-0.78</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="27">
         <v>-6.97</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="35">
         <v>-8.32</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="39">
         <v>-7.89</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="28">
         <v>-7.79</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="31">
         <v>1.42</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="29">
         <v>3.29</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="36">
         <v>10.45</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="32">
         <v>15.53</v>
       </c>
-      <c r="Q4" s="38">
+      <c r="Q4" s="33">
         <v>12.95</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="37">
         <v>13.61</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="34">
         <v>11.08</v>
       </c>
-      <c r="T4" s="32">
+      <c r="T4" s="38">
         <v>22.39</v>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       <c r="C5" t="str">
         <v>002856</v>
       </c>
-      <c r="D5" s="47" t="str">
+      <c r="D5" s="51" t="str">
         <v>净买: 382.36万</v>
       </c>
       <c r="E5">
@@ -4307,40 +4307,40 @@
       <c r="H5">
         <v>0.25</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="48">
         <v>-10</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="52">
         <v>-0.99</v>
       </c>
       <c r="K5" s="44">
         <v>-1.82</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="40">
         <v>-10.66</v>
       </c>
-      <c r="M5" s="46">
+      <c r="M5" s="41">
         <v>-12.81</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="45">
         <v>-10.33</v>
       </c>
-      <c r="O5" s="49">
+      <c r="O5" s="42">
         <v>-9.92</v>
       </c>
-      <c r="P5" s="50">
+      <c r="P5" s="46">
         <v>-11.24</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="49">
         <v>-10.25</v>
       </c>
-      <c r="R5" s="41">
+      <c r="R5" s="43">
         <v>-11.07</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="47">
         <v>-12.73</v>
       </c>
-      <c r="T5" s="51">
+      <c r="T5" s="50">
         <v>-4.55</v>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       <c r="C6" t="str">
         <v>001331</v>
       </c>
-      <c r="D6" s="60" t="str">
+      <c r="D6" s="53" t="str">
         <v>净买: 966.34万</v>
       </c>
       <c r="E6">
@@ -4369,37 +4369,37 @@
       <c r="H6">
         <v>10.01</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="54">
         <v>0</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="55">
         <v>-9.55</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="60">
         <v>-18.58</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="56">
         <v>-22.16</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="63">
         <v>-22.81</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="61">
         <v>-22.42</v>
       </c>
-      <c r="O6" s="62">
+      <c r="O6" s="57">
         <v>-22.29</v>
       </c>
-      <c r="P6" s="65">
+      <c r="P6" s="58">
         <v>-22.03</v>
       </c>
-      <c r="Q6" s="63">
+      <c r="Q6" s="62">
         <v>-18.52</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="64">
         <v>-16.83</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="65">
         <v>-16.76</v>
       </c>
       <c r="T6" s="59">
@@ -4416,7 +4416,7 @@
       <c r="C7" t="str">
         <v>605169</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="68" t="str">
         <v>净卖: -1118.05万</v>
       </c>
       <c r="E7">
@@ -4431,40 +4431,40 @@
       <c r="H7">
         <v>-4.72</v>
       </c>
-      <c r="I7" s="78">
+      <c r="I7" s="74">
         <v>15.46</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="71">
         <v>12.98</v>
       </c>
-      <c r="K7" s="74">
+      <c r="K7" s="75">
         <v>2.95</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="76">
         <v>-4.72</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="77">
         <v>-3.13</v>
       </c>
-      <c r="N7" s="68">
+      <c r="N7" s="69">
         <v>-5.78</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="78">
         <v>-5.01</v>
       </c>
       <c r="P7" s="72">
         <v>-6.43</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="70">
         <v>-10.5</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="66">
         <v>-9.79</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="73">
         <v>-11.15</v>
       </c>
-      <c r="T7" s="70">
+      <c r="T7" s="67">
         <v>-28.26</v>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       <c r="C8" t="str">
         <v>836699</v>
       </c>
-      <c r="D8" s="86" t="str">
+      <c r="D8" s="83" t="str">
         <v>净卖: -801.39万</v>
       </c>
       <c r="E8">
@@ -4493,37 +4493,37 @@
       <c r="H8">
         <v>1.68</v>
       </c>
-      <c r="I8" s="82">
+      <c r="I8" s="88">
         <v>27.86</v>
       </c>
-      <c r="J8" s="87">
+      <c r="J8" s="84">
         <v>25.31</v>
       </c>
-      <c r="K8" s="83">
+      <c r="K8" s="89">
         <v>20.9</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="85">
         <v>14.59</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="80">
         <v>31.58</v>
       </c>
-      <c r="N8" s="85">
+      <c r="N8" s="86">
         <v>29.44</v>
       </c>
-      <c r="O8" s="88">
+      <c r="O8" s="81">
         <v>22.64</v>
       </c>
-      <c r="P8" s="90">
+      <c r="P8" s="79">
         <v>24.9</v>
       </c>
-      <c r="Q8" s="80">
+      <c r="Q8" s="82">
         <v>20.99</v>
       </c>
-      <c r="R8" s="81">
+      <c r="R8" s="87">
         <v>18.14</v>
       </c>
-      <c r="S8" s="89">
+      <c r="S8" s="90">
         <v>36.74</v>
       </c>
       <c r="T8" s="91">
@@ -4540,7 +4540,7 @@
       <c r="C9" t="str">
         <v>301632</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="100" t="str">
         <v>净买: 2340.61万</v>
       </c>
       <c r="E9">
@@ -4555,37 +4555,37 @@
       <c r="H9">
         <v>2.77</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="104">
         <v>-13.93</v>
       </c>
-      <c r="J9" s="102">
+      <c r="J9" s="92">
         <v>-17.96</v>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="96">
         <v>-18.95</v>
       </c>
       <c r="L9" s="93">
         <v>-17</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="101">
         <v>-21.23</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="102">
         <v>-26.34</v>
       </c>
-      <c r="O9" s="99">
+      <c r="O9" s="94">
         <v>-26.39</v>
       </c>
-      <c r="P9" s="104">
+      <c r="P9" s="97">
         <v>-25.82</v>
       </c>
-      <c r="Q9" s="100">
+      <c r="Q9" s="103">
         <v>-28.19</v>
       </c>
-      <c r="R9" s="92">
+      <c r="R9" s="98">
         <v>-30.97</v>
       </c>
-      <c r="S9" s="94">
+      <c r="S9" s="99">
         <v>-30.82</v>
       </c>
       <c r="T9" s="95">
@@ -4602,7 +4602,7 @@
       <c r="C10" t="str">
         <v>300948</v>
       </c>
-      <c r="D10" s="110" t="str">
+      <c r="D10" s="106" t="str">
         <v>净卖: -709.60万</v>
       </c>
       <c r="E10">
@@ -4617,40 +4617,40 @@
       <c r="H10">
         <v>2.78</v>
       </c>
-      <c r="I10" s="107">
+      <c r="I10" s="110">
         <v>16.75</v>
       </c>
-      <c r="J10" s="108">
+      <c r="J10" s="107">
         <v>1.59</v>
       </c>
-      <c r="K10" s="117">
+      <c r="K10" s="112">
         <v>0.16</v>
       </c>
-      <c r="L10" s="111">
+      <c r="L10" s="113">
         <v>-2.23</v>
       </c>
-      <c r="M10" s="115">
+      <c r="M10" s="114">
         <v>5.35</v>
       </c>
-      <c r="N10" s="109">
+      <c r="N10" s="115">
         <v>8.32</v>
       </c>
-      <c r="O10" s="116">
+      <c r="O10" s="108">
         <v>9.38</v>
       </c>
-      <c r="P10" s="112">
+      <c r="P10" s="116">
         <v>10.44</v>
       </c>
-      <c r="Q10" s="113">
+      <c r="Q10" s="109">
         <v>8.64</v>
       </c>
-      <c r="R10" s="114">
+      <c r="R10" s="111">
         <v>4.13</v>
       </c>
-      <c r="S10" s="105">
+      <c r="S10" s="117">
         <v>3.34</v>
       </c>
-      <c r="T10" s="106">
+      <c r="T10" s="105">
         <v>2.28</v>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       <c r="C11" t="str">
         <v>000069</v>
       </c>
-      <c r="D11" s="130" t="str">
+      <c r="D11" s="125" t="str">
         <v>净买: 3152.70万</v>
       </c>
       <c r="E11">
@@ -4679,40 +4679,40 @@
       <c r="H11">
         <v>1.88</v>
       </c>
-      <c r="I11" s="127">
+      <c r="I11" s="118">
         <v>8.12</v>
       </c>
-      <c r="J11" s="123">
+      <c r="J11" s="119">
         <v>3.69</v>
       </c>
-      <c r="K11" s="122">
+      <c r="K11" s="126">
         <v>4.06</v>
       </c>
-      <c r="L11" s="118">
+      <c r="L11" s="122">
         <v>2.95</v>
       </c>
-      <c r="M11" s="124">
+      <c r="M11" s="120">
         <v>4.8</v>
       </c>
-      <c r="N11" s="125">
+      <c r="N11" s="123">
         <v>0.37</v>
       </c>
-      <c r="O11" s="128">
+      <c r="O11" s="127">
         <v>-2.95</v>
       </c>
-      <c r="P11" s="119">
+      <c r="P11" s="128">
         <v>0</v>
       </c>
-      <c r="Q11" s="126">
+      <c r="Q11" s="121">
         <v>-1.11</v>
       </c>
-      <c r="R11" s="129">
+      <c r="R11" s="124">
         <v>-1.85</v>
       </c>
-      <c r="S11" s="120">
+      <c r="S11" s="129">
         <v>0</v>
       </c>
-      <c r="T11" s="121">
+      <c r="T11" s="130">
         <v>-17.71</v>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       <c r="C12" t="str">
         <v>002242</v>
       </c>
-      <c r="D12" s="137" t="str">
+      <c r="D12" s="142" t="str">
         <v>净卖: -1077.90万</v>
       </c>
       <c r="E12">
@@ -4741,40 +4741,40 @@
       <c r="H12">
         <v>10.04</v>
       </c>
-      <c r="I12" s="143">
+      <c r="I12" s="131">
         <v>0</v>
       </c>
-      <c r="J12" s="133">
+      <c r="J12" s="139">
         <v>-4.93</v>
       </c>
-      <c r="K12" s="136">
+      <c r="K12" s="143">
         <v>-3.04</v>
       </c>
-      <c r="L12" s="138">
+      <c r="L12" s="132">
         <v>-11.42</v>
       </c>
-      <c r="M12" s="134">
+      <c r="M12" s="135">
         <v>-11.83</v>
       </c>
-      <c r="N12" s="135">
+      <c r="N12" s="136">
         <v>-15.61</v>
       </c>
-      <c r="O12" s="139">
+      <c r="O12" s="140">
         <v>-15.12</v>
       </c>
-      <c r="P12" s="131">
+      <c r="P12" s="137">
         <v>-14.71</v>
       </c>
-      <c r="Q12" s="140">
+      <c r="Q12" s="138">
         <v>-15.37</v>
       </c>
       <c r="R12" s="141">
         <v>-14.13</v>
       </c>
-      <c r="S12" s="142">
+      <c r="S12" s="133">
         <v>-14.13</v>
       </c>
-      <c r="T12" s="132">
+      <c r="T12" s="134">
         <v>-15.94</v>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
       <c r="C13" t="str">
         <v>603877</v>
       </c>
-      <c r="D13" s="147" t="str">
+      <c r="D13" s="150" t="str">
         <v>净卖: -596.03万</v>
       </c>
       <c r="E13">
@@ -4803,40 +4803,40 @@
       <c r="H13">
         <v>3.85</v>
       </c>
-      <c r="I13" s="148">
+      <c r="I13" s="151">
         <v>5.94</v>
       </c>
-      <c r="J13" s="145">
+      <c r="J13" s="152">
         <v>0</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="156">
         <v>-6.18</v>
       </c>
-      <c r="L13" s="149">
+      <c r="L13" s="153">
         <v>-4.29</v>
       </c>
-      <c r="M13" s="154">
+      <c r="M13" s="149">
         <v>-4.94</v>
       </c>
-      <c r="N13" s="150">
+      <c r="N13" s="144">
         <v>-5</v>
       </c>
-      <c r="O13" s="144">
+      <c r="O13" s="154">
         <v>-7.41</v>
       </c>
-      <c r="P13" s="151">
+      <c r="P13" s="146">
         <v>-3.76</v>
       </c>
       <c r="Q13" s="155">
         <v>-4.12</v>
       </c>
-      <c r="R13" s="152">
+      <c r="R13" s="147">
         <v>-4.24</v>
       </c>
-      <c r="S13" s="153">
+      <c r="S13" s="148">
         <v>-5.88</v>
       </c>
-      <c r="T13" s="156">
+      <c r="T13" s="145">
         <v>-13.41</v>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       <c r="C14" t="str">
         <v>603216</v>
       </c>
-      <c r="D14" s="163" t="str">
+      <c r="D14" s="165" t="str">
         <v>净买: 462.51万</v>
       </c>
       <c r="E14">
@@ -4865,40 +4865,40 @@
       <c r="H14">
         <v>-6.54</v>
       </c>
-      <c r="I14" s="164">
+      <c r="I14" s="160">
         <v>-3.72</v>
       </c>
-      <c r="J14" s="157">
+      <c r="J14" s="166">
         <v>-9.38</v>
       </c>
-      <c r="K14" s="158">
+      <c r="K14" s="167">
         <v>-2.23</v>
       </c>
-      <c r="L14" s="160">
+      <c r="L14" s="161">
         <v>-4.26</v>
       </c>
-      <c r="M14" s="165">
+      <c r="M14" s="157">
         <v>-0.51</v>
       </c>
-      <c r="N14" s="166">
+      <c r="N14" s="162">
         <v>9.31</v>
       </c>
-      <c r="O14" s="169">
+      <c r="O14" s="168">
         <v>5.63</v>
       </c>
-      <c r="P14" s="167">
+      <c r="P14" s="163">
         <v>5.63</v>
       </c>
-      <c r="Q14" s="159">
+      <c r="Q14" s="158">
         <v>11.51</v>
       </c>
-      <c r="R14" s="161">
+      <c r="R14" s="169">
         <v>11.89</v>
       </c>
-      <c r="S14" s="162">
+      <c r="S14" s="159">
         <v>2.92</v>
       </c>
-      <c r="T14" s="168">
+      <c r="T14" s="164">
         <v>-3.69</v>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       <c r="C15" t="str">
         <v>002589</v>
       </c>
-      <c r="D15" s="171" t="str">
+      <c r="D15" s="182" t="str">
         <v>净买: 1428.73万</v>
       </c>
       <c r="E15">
@@ -4927,40 +4927,40 @@
       <c r="H15">
         <v>-5.54</v>
       </c>
-      <c r="I15" s="179">
+      <c r="I15" s="176">
         <v>-4.74</v>
       </c>
-      <c r="J15" s="175">
+      <c r="J15" s="178">
         <v>-11.96</v>
       </c>
-      <c r="K15" s="172">
+      <c r="K15" s="170">
         <v>-19.86</v>
       </c>
-      <c r="L15" s="180">
+      <c r="L15" s="171">
         <v>-20.77</v>
       </c>
-      <c r="M15" s="176">
+      <c r="M15" s="172">
         <v>-18.96</v>
       </c>
-      <c r="N15" s="181">
+      <c r="N15" s="180">
         <v>-23.25</v>
       </c>
-      <c r="O15" s="177">
+      <c r="O15" s="173">
         <v>-23.7</v>
       </c>
-      <c r="P15" s="182">
+      <c r="P15" s="181">
         <v>-20.77</v>
       </c>
-      <c r="Q15" s="178">
+      <c r="Q15" s="179">
         <v>-19.86</v>
       </c>
-      <c r="R15" s="173">
+      <c r="R15" s="174">
         <v>-20.32</v>
       </c>
-      <c r="S15" s="174">
+      <c r="S15" s="175">
         <v>-22.8</v>
       </c>
-      <c r="T15" s="170">
+      <c r="T15" s="177">
         <v>-22.57</v>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       <c r="C16" t="str">
         <v>605255</v>
       </c>
-      <c r="D16" s="193" t="str">
+      <c r="D16" s="184" t="str">
         <v>净卖: -745.64万</v>
       </c>
       <c r="E16">
@@ -4989,40 +4989,40 @@
       <c r="H16">
         <v>-10</v>
       </c>
-      <c r="I16" s="191">
+      <c r="I16" s="194">
         <v>0</v>
       </c>
-      <c r="J16" s="192">
+      <c r="J16" s="191">
         <v>-10</v>
       </c>
-      <c r="K16" s="194">
+      <c r="K16" s="185">
         <v>-1</v>
       </c>
-      <c r="L16" s="185">
+      <c r="L16" s="186">
         <v>-10.9</v>
       </c>
       <c r="M16" s="195">
         <v>-17.03</v>
       </c>
-      <c r="N16" s="190">
+      <c r="N16" s="187">
         <v>-11.34</v>
       </c>
-      <c r="O16" s="183">
+      <c r="O16" s="188">
         <v>-8.27</v>
       </c>
-      <c r="P16" s="186">
+      <c r="P16" s="183">
         <v>-9.76</v>
       </c>
-      <c r="Q16" s="187">
+      <c r="Q16" s="192">
         <v>-11.21</v>
       </c>
-      <c r="R16" s="184">
+      <c r="R16" s="189">
         <v>-12.68</v>
       </c>
-      <c r="S16" s="188">
+      <c r="S16" s="190">
         <v>-21.41</v>
       </c>
-      <c r="T16" s="189">
+      <c r="T16" s="193">
         <v>-38.91</v>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       <c r="C17" t="str">
         <v>601139</v>
       </c>
-      <c r="D17" s="202" t="str">
+      <c r="D17" s="205" t="str">
         <v>净卖: -3779.77万</v>
       </c>
       <c r="E17">
@@ -5051,40 +5051,40 @@
       <c r="H17">
         <v>1.68</v>
       </c>
-      <c r="I17" s="197">
+      <c r="I17" s="201">
         <v>8.25</v>
       </c>
-      <c r="J17" s="205">
+      <c r="J17" s="204">
         <v>0.41</v>
       </c>
-      <c r="K17" s="206">
+      <c r="K17" s="197">
         <v>-3.58</v>
       </c>
-      <c r="L17" s="207">
+      <c r="L17" s="198">
         <v>-3.03</v>
       </c>
-      <c r="M17" s="208">
+      <c r="M17" s="202">
         <v>-0.55</v>
       </c>
-      <c r="N17" s="200">
+      <c r="N17" s="203">
         <v>-1.79</v>
       </c>
-      <c r="O17" s="203">
+      <c r="O17" s="199">
         <v>-0.41</v>
       </c>
-      <c r="P17" s="198">
+      <c r="P17" s="200">
         <v>7.7</v>
       </c>
-      <c r="Q17" s="204">
+      <c r="Q17" s="206">
         <v>5.23</v>
       </c>
-      <c r="R17" s="196">
+      <c r="R17" s="207">
         <v>3.03</v>
       </c>
-      <c r="S17" s="199">
+      <c r="S17" s="208">
         <v>0</v>
       </c>
-      <c r="T17" s="201">
+      <c r="T17" s="196">
         <v>-6.46</v>
       </c>
     </row>
@@ -5147,40 +5147,40 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="216">
+      <c r="I19" s="214">
         <v>43.75</v>
       </c>
-      <c r="J19" s="217">
+      <c r="J19" s="209">
         <v>31.25</v>
       </c>
-      <c r="K19" s="209">
+      <c r="K19" s="219">
         <v>25</v>
       </c>
       <c r="L19" s="215">
         <v>18.75</v>
       </c>
-      <c r="M19" s="212">
+      <c r="M19" s="216">
         <v>31.25</v>
       </c>
-      <c r="N19" s="210">
+      <c r="N19" s="217">
         <v>37.5</v>
       </c>
-      <c r="O19" s="218">
+      <c r="O19" s="220">
         <v>31.25</v>
       </c>
-      <c r="P19" s="219">
+      <c r="P19" s="210">
         <v>37.5</v>
       </c>
       <c r="Q19" s="211">
         <v>37.5</v>
       </c>
-      <c r="R19" s="213">
+      <c r="R19" s="218">
         <v>37.5</v>
       </c>
-      <c r="S19" s="220">
+      <c r="S19" s="212">
         <v>31.25</v>
       </c>
-      <c r="T19" s="214">
+      <c r="T19" s="213">
         <v>37.5</v>
       </c>
     </row>
@@ -5195,40 +5195,40 @@
       <c r="F20" t="str"/>
       <c r="G20" t="str"/>
       <c r="H20" t="str"/>
-      <c r="I20" s="227">
+      <c r="I20" s="226">
         <v>3.11</v>
       </c>
       <c r="J20" s="229">
         <v>-2.73</v>
       </c>
-      <c r="K20" s="224">
+      <c r="K20" s="230">
         <v>-4.91</v>
       </c>
-      <c r="L20" s="230">
+      <c r="L20" s="231">
         <v>-7.8</v>
       </c>
-      <c r="M20" s="225">
+      <c r="M20" s="223">
         <v>-5.55</v>
       </c>
-      <c r="N20" s="222">
+      <c r="N20" s="227">
         <v>-5.78</v>
       </c>
-      <c r="O20" s="231">
+      <c r="O20" s="232">
         <v>-6.29</v>
       </c>
-      <c r="P20" s="228">
+      <c r="P20" s="224">
         <v>-4.87</v>
       </c>
-      <c r="Q20" s="232">
+      <c r="Q20" s="228">
         <v>-5.25</v>
       </c>
       <c r="R20" s="221">
         <v>-5.94</v>
       </c>
-      <c r="S20" s="226">
+      <c r="S20" s="225">
         <v>-6.59</v>
       </c>
-      <c r="T20" s="223">
+      <c r="T20" s="222">
         <v>32.72</v>
       </c>
     </row>

--- a/youzi/金田路/index.xlsx
+++ b/youzi/金田路/index.xlsx
@@ -39,66 +39,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -111,12 +75,114 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15361"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -129,7 +195,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,19 +207,499 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
+        <fgColor rgb="FFE77A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAE55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C78A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77882"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA2AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,13 +711,223 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD83343"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15361"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBC73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2AA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,31 +939,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77A84"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,7 +963,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
+        <fgColor rgb="FF4DB665"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -237,1158 +1017,360 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA2AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77882"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBC73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2AA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4DB665"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBE2736"/>
         <bgColor/>
       </patternFill>
@@ -1407,7 +1389,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4106,7 +4106,7 @@
       <c r="C2" t="str">
         <v>603124</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="4" t="str">
         <v>净买: 3338.76万</v>
       </c>
       <c r="E2">
@@ -4121,40 +4121,40 @@
       <c r="H2">
         <v>526.19</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="5">
         <v>12.88</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="10">
         <v>-12.55</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="11">
         <v>-22.7</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="6">
         <v>-26.47</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="12">
         <v>-25.17</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="13">
         <v>-30.67</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="1">
         <v>-32.55</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="2">
         <v>-31.88</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="9">
         <v>-29.12</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="7">
         <v>-30.52</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="3">
         <v>-28.5</v>
       </c>
-      <c r="T2" s="13">
+      <c r="T2" s="8">
         <v>87.91</v>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       <c r="C3" t="str">
         <v>605298</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="21" t="str">
         <v>净卖: -183.82万</v>
       </c>
       <c r="E3">
@@ -4183,40 +4183,40 @@
       <c r="H3">
         <v>-4.14</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="16">
         <v>-6.15</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="22">
         <v>-1.99</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="23">
         <v>-0.75</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="18">
         <v>3.41</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="17">
         <v>7.06</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="19">
         <v>9.39</v>
       </c>
-      <c r="O3" s="22">
+      <c r="O3" s="24">
         <v>5.32</v>
       </c>
-      <c r="P3" s="23">
+      <c r="P3" s="20">
         <v>4.24</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="25">
         <v>4.98</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="26">
         <v>6.56</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="14">
         <v>4.73</v>
       </c>
-      <c r="T3" s="18">
+      <c r="T3" s="15">
         <v>354.73</v>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       <c r="C4" t="str">
         <v>600418</v>
       </c>
-      <c r="D4" s="30" t="str">
+      <c r="D4" s="28" t="str">
         <v>净卖: -8419.55万</v>
       </c>
       <c r="E4">
@@ -4245,40 +4245,40 @@
       <c r="H4">
         <v>-0.78</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="29">
         <v>-6.97</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="30">
         <v>-8.32</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="31">
         <v>-7.89</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="32">
         <v>-7.79</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="33">
         <v>1.42</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="35">
         <v>3.29</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="37">
         <v>10.45</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="38">
         <v>15.53</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="39">
         <v>12.95</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="27">
         <v>13.61</v>
       </c>
       <c r="S4" s="34">
         <v>11.08</v>
       </c>
-      <c r="T4" s="38">
+      <c r="T4" s="36">
         <v>22.39</v>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       <c r="C5" t="str">
         <v>002856</v>
       </c>
-      <c r="D5" s="51" t="str">
+      <c r="D5" s="47" t="str">
         <v>净买: 382.36万</v>
       </c>
       <c r="E5">
@@ -4307,40 +4307,40 @@
       <c r="H5">
         <v>0.25</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="50">
         <v>-10</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5" s="45">
         <v>-0.99</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="48">
         <v>-1.82</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="41">
         <v>-10.66</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="42">
         <v>-12.81</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="43">
         <v>-10.33</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="46">
         <v>-9.92</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="44">
         <v>-11.24</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="51">
         <v>-10.25</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="49">
         <v>-11.07</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="52">
         <v>-12.73</v>
       </c>
-      <c r="T5" s="50">
+      <c r="T5" s="40">
         <v>-4.55</v>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       <c r="C6" t="str">
         <v>001331</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="59" t="str">
         <v>净买: 966.34万</v>
       </c>
       <c r="E6">
@@ -4369,40 +4369,40 @@
       <c r="H6">
         <v>10.01</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="64">
         <v>0</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="60">
         <v>-9.55</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="65">
         <v>-18.58</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="61">
         <v>-22.16</v>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="53">
         <v>-22.81</v>
       </c>
-      <c r="N6" s="61">
+      <c r="N6" s="54">
         <v>-22.42</v>
       </c>
-      <c r="O6" s="57">
+      <c r="O6" s="62">
         <v>-22.29</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="63">
         <v>-22.03</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="55">
         <v>-18.52</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="56">
         <v>-16.83</v>
       </c>
-      <c r="S6" s="65">
+      <c r="S6" s="57">
         <v>-16.76</v>
       </c>
-      <c r="T6" s="59">
+      <c r="T6" s="58">
         <v>231.12</v>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       <c r="C7" t="str">
         <v>605169</v>
       </c>
-      <c r="D7" s="68" t="str">
+      <c r="D7" s="70" t="str">
         <v>净卖: -1118.05万</v>
       </c>
       <c r="E7">
@@ -4437,34 +4437,34 @@
       <c r="J7" s="71">
         <v>12.98</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="68">
         <v>2.95</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="75">
         <v>-4.72</v>
       </c>
       <c r="M7" s="77">
         <v>-3.13</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="72">
         <v>-5.78</v>
       </c>
       <c r="O7" s="78">
         <v>-5.01</v>
       </c>
-      <c r="P7" s="72">
+      <c r="P7" s="73">
         <v>-6.43</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="66">
         <v>-10.5</v>
       </c>
-      <c r="R7" s="66">
+      <c r="R7" s="76">
         <v>-9.79</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="67">
         <v>-11.15</v>
       </c>
-      <c r="T7" s="67">
+      <c r="T7" s="69">
         <v>-28.26</v>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       <c r="C8" t="str">
         <v>836699</v>
       </c>
-      <c r="D8" s="83" t="str">
+      <c r="D8" s="89" t="str">
         <v>净卖: -801.39万</v>
       </c>
       <c r="E8">
@@ -4493,40 +4493,40 @@
       <c r="H8">
         <v>1.68</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="80">
         <v>27.86</v>
       </c>
-      <c r="J8" s="84">
+      <c r="J8" s="83">
         <v>25.31</v>
       </c>
-      <c r="K8" s="89">
+      <c r="K8" s="87">
         <v>20.9</v>
       </c>
-      <c r="L8" s="85">
+      <c r="L8" s="81">
         <v>14.59</v>
       </c>
-      <c r="M8" s="80">
+      <c r="M8" s="90">
         <v>31.58</v>
       </c>
-      <c r="N8" s="86">
+      <c r="N8" s="91">
         <v>29.44</v>
       </c>
-      <c r="O8" s="81">
+      <c r="O8" s="84">
         <v>22.64</v>
       </c>
-      <c r="P8" s="79">
+      <c r="P8" s="82">
         <v>24.9</v>
       </c>
-      <c r="Q8" s="82">
+      <c r="Q8" s="79">
         <v>20.99</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="88">
         <v>18.14</v>
       </c>
-      <c r="S8" s="90">
+      <c r="S8" s="85">
         <v>36.74</v>
       </c>
-      <c r="T8" s="91">
+      <c r="T8" s="86">
         <v>30.08</v>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       <c r="C9" t="str">
         <v>301632</v>
       </c>
-      <c r="D9" s="100" t="str">
+      <c r="D9" s="104" t="str">
         <v>净买: 2340.61万</v>
       </c>
       <c r="E9">
@@ -4555,40 +4555,40 @@
       <c r="H9">
         <v>2.77</v>
       </c>
-      <c r="I9" s="104">
+      <c r="I9" s="92">
         <v>-13.93</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="100">
         <v>-17.96</v>
       </c>
-      <c r="K9" s="96">
+      <c r="K9" s="94">
         <v>-18.95</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="101">
         <v>-17</v>
       </c>
-      <c r="M9" s="101">
+      <c r="M9" s="95">
         <v>-21.23</v>
       </c>
       <c r="N9" s="102">
         <v>-26.34</v>
       </c>
-      <c r="O9" s="94">
+      <c r="O9" s="96">
         <v>-26.39</v>
       </c>
-      <c r="P9" s="97">
+      <c r="P9" s="103">
         <v>-25.82</v>
       </c>
-      <c r="Q9" s="103">
+      <c r="Q9" s="97">
         <v>-28.19</v>
       </c>
-      <c r="R9" s="98">
+      <c r="R9" s="93">
         <v>-30.97</v>
       </c>
-      <c r="S9" s="99">
+      <c r="S9" s="98">
         <v>-30.82</v>
       </c>
-      <c r="T9" s="95">
+      <c r="T9" s="99">
         <v>-53.45</v>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       <c r="C10" t="str">
         <v>300948</v>
       </c>
-      <c r="D10" s="106" t="str">
+      <c r="D10" s="113" t="str">
         <v>净卖: -709.60万</v>
       </c>
       <c r="E10">
@@ -4617,40 +4617,40 @@
       <c r="H10">
         <v>2.78</v>
       </c>
-      <c r="I10" s="110">
+      <c r="I10" s="114">
         <v>16.75</v>
       </c>
-      <c r="J10" s="107">
+      <c r="J10" s="110">
         <v>1.59</v>
       </c>
-      <c r="K10" s="112">
+      <c r="K10" s="111">
         <v>0.16</v>
       </c>
-      <c r="L10" s="113">
+      <c r="L10" s="115">
         <v>-2.23</v>
       </c>
-      <c r="M10" s="114">
+      <c r="M10" s="116">
         <v>5.35</v>
       </c>
-      <c r="N10" s="115">
+      <c r="N10" s="106">
         <v>8.32</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="112">
         <v>9.38</v>
       </c>
-      <c r="P10" s="116">
+      <c r="P10" s="117">
         <v>10.44</v>
       </c>
-      <c r="Q10" s="109">
+      <c r="Q10" s="107">
         <v>8.64</v>
       </c>
-      <c r="R10" s="111">
+      <c r="R10" s="105">
         <v>4.13</v>
       </c>
-      <c r="S10" s="117">
+      <c r="S10" s="108">
         <v>3.34</v>
       </c>
-      <c r="T10" s="105">
+      <c r="T10" s="109">
         <v>2.28</v>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       <c r="C11" t="str">
         <v>000069</v>
       </c>
-      <c r="D11" s="125" t="str">
+      <c r="D11" s="120" t="str">
         <v>净买: 3152.70万</v>
       </c>
       <c r="E11">
@@ -4679,40 +4679,40 @@
       <c r="H11">
         <v>1.88</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="130">
         <v>8.12</v>
       </c>
-      <c r="J11" s="119">
+      <c r="J11" s="125">
         <v>3.69</v>
       </c>
-      <c r="K11" s="126">
+      <c r="K11" s="119">
         <v>4.06</v>
       </c>
-      <c r="L11" s="122">
+      <c r="L11" s="121">
         <v>2.95</v>
       </c>
-      <c r="M11" s="120">
+      <c r="M11" s="118">
         <v>4.8</v>
       </c>
-      <c r="N11" s="123">
+      <c r="N11" s="122">
         <v>0.37</v>
       </c>
-      <c r="O11" s="127">
+      <c r="O11" s="123">
         <v>-2.95</v>
       </c>
-      <c r="P11" s="128">
+      <c r="P11" s="124">
         <v>0</v>
       </c>
-      <c r="Q11" s="121">
+      <c r="Q11" s="126">
         <v>-1.11</v>
       </c>
-      <c r="R11" s="124">
+      <c r="R11" s="127">
         <v>-1.85</v>
       </c>
-      <c r="S11" s="129">
+      <c r="S11" s="128">
         <v>0</v>
       </c>
-      <c r="T11" s="130">
+      <c r="T11" s="129">
         <v>-17.71</v>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       <c r="C12" t="str">
         <v>002242</v>
       </c>
-      <c r="D12" s="142" t="str">
+      <c r="D12" s="139" t="str">
         <v>净卖: -1077.90万</v>
       </c>
       <c r="E12">
@@ -4741,40 +4741,40 @@
       <c r="H12">
         <v>10.04</v>
       </c>
-      <c r="I12" s="131">
+      <c r="I12" s="135">
         <v>0</v>
       </c>
-      <c r="J12" s="139">
+      <c r="J12" s="140">
         <v>-4.93</v>
       </c>
-      <c r="K12" s="143">
+      <c r="K12" s="133">
         <v>-3.04</v>
       </c>
-      <c r="L12" s="132">
+      <c r="L12" s="143">
         <v>-11.42</v>
       </c>
-      <c r="M12" s="135">
+      <c r="M12" s="141">
         <v>-11.83</v>
       </c>
-      <c r="N12" s="136">
+      <c r="N12" s="134">
         <v>-15.61</v>
       </c>
-      <c r="O12" s="140">
+      <c r="O12" s="142">
         <v>-15.12</v>
       </c>
-      <c r="P12" s="137">
+      <c r="P12" s="136">
         <v>-14.71</v>
       </c>
-      <c r="Q12" s="138">
+      <c r="Q12" s="137">
         <v>-15.37</v>
       </c>
-      <c r="R12" s="141">
+      <c r="R12" s="138">
         <v>-14.13</v>
       </c>
-      <c r="S12" s="133">
+      <c r="S12" s="131">
         <v>-14.13</v>
       </c>
-      <c r="T12" s="134">
+      <c r="T12" s="132">
         <v>-15.94</v>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
       <c r="C13" t="str">
         <v>603877</v>
       </c>
-      <c r="D13" s="150" t="str">
+      <c r="D13" s="156" t="str">
         <v>净卖: -596.03万</v>
       </c>
       <c r="E13">
@@ -4803,40 +4803,40 @@
       <c r="H13">
         <v>3.85</v>
       </c>
-      <c r="I13" s="151">
+      <c r="I13" s="152">
         <v>5.94</v>
       </c>
-      <c r="J13" s="152">
+      <c r="J13" s="147">
         <v>0</v>
       </c>
-      <c r="K13" s="156">
+      <c r="K13" s="150">
         <v>-6.18</v>
       </c>
       <c r="L13" s="153">
         <v>-4.29</v>
       </c>
-      <c r="M13" s="149">
+      <c r="M13" s="148">
         <v>-4.94</v>
       </c>
-      <c r="N13" s="144">
+      <c r="N13" s="154">
         <v>-5</v>
       </c>
-      <c r="O13" s="154">
+      <c r="O13" s="149">
         <v>-7.41</v>
       </c>
-      <c r="P13" s="146">
+      <c r="P13" s="144">
         <v>-3.76</v>
       </c>
       <c r="Q13" s="155">
         <v>-4.12</v>
       </c>
-      <c r="R13" s="147">
+      <c r="R13" s="145">
         <v>-4.24</v>
       </c>
-      <c r="S13" s="148">
+      <c r="S13" s="146">
         <v>-5.88</v>
       </c>
-      <c r="T13" s="145">
+      <c r="T13" s="151">
         <v>-13.41</v>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       <c r="C14" t="str">
         <v>603216</v>
       </c>
-      <c r="D14" s="165" t="str">
+      <c r="D14" s="157" t="str">
         <v>净买: 462.51万</v>
       </c>
       <c r="E14">
@@ -4865,40 +4865,40 @@
       <c r="H14">
         <v>-6.54</v>
       </c>
-      <c r="I14" s="160">
+      <c r="I14" s="168">
         <v>-3.72</v>
       </c>
       <c r="J14" s="166">
         <v>-9.38</v>
       </c>
-      <c r="K14" s="167">
+      <c r="K14" s="164">
         <v>-2.23</v>
       </c>
-      <c r="L14" s="161">
+      <c r="L14" s="158">
         <v>-4.26</v>
       </c>
-      <c r="M14" s="157">
+      <c r="M14" s="159">
         <v>-0.51</v>
       </c>
-      <c r="N14" s="162">
+      <c r="N14" s="160">
         <v>9.31</v>
       </c>
-      <c r="O14" s="168">
+      <c r="O14" s="167">
         <v>5.63</v>
       </c>
-      <c r="P14" s="163">
+      <c r="P14" s="161">
         <v>5.63</v>
       </c>
-      <c r="Q14" s="158">
+      <c r="Q14" s="162">
         <v>11.51</v>
       </c>
-      <c r="R14" s="169">
+      <c r="R14" s="163">
         <v>11.89</v>
       </c>
-      <c r="S14" s="159">
+      <c r="S14" s="169">
         <v>2.92</v>
       </c>
-      <c r="T14" s="164">
+      <c r="T14" s="165">
         <v>-3.69</v>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       <c r="C15" t="str">
         <v>002589</v>
       </c>
-      <c r="D15" s="182" t="str">
+      <c r="D15" s="174" t="str">
         <v>净买: 1428.73万</v>
       </c>
       <c r="E15">
@@ -4927,40 +4927,40 @@
       <c r="H15">
         <v>-5.54</v>
       </c>
-      <c r="I15" s="176">
+      <c r="I15" s="173">
         <v>-4.74</v>
       </c>
       <c r="J15" s="178">
         <v>-11.96</v>
       </c>
-      <c r="K15" s="170">
+      <c r="K15" s="175">
         <v>-19.86</v>
       </c>
-      <c r="L15" s="171">
+      <c r="L15" s="182">
         <v>-20.77</v>
       </c>
-      <c r="M15" s="172">
+      <c r="M15" s="170">
         <v>-18.96</v>
       </c>
-      <c r="N15" s="180">
+      <c r="N15" s="176">
         <v>-23.25</v>
       </c>
-      <c r="O15" s="173">
+      <c r="O15" s="179">
         <v>-23.7</v>
       </c>
-      <c r="P15" s="181">
+      <c r="P15" s="177">
         <v>-20.77</v>
       </c>
-      <c r="Q15" s="179">
+      <c r="Q15" s="180">
         <v>-19.86</v>
       </c>
-      <c r="R15" s="174">
+      <c r="R15" s="171">
         <v>-20.32</v>
       </c>
-      <c r="S15" s="175">
+      <c r="S15" s="181">
         <v>-22.8</v>
       </c>
-      <c r="T15" s="177">
+      <c r="T15" s="172">
         <v>-22.57</v>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       <c r="C16" t="str">
         <v>605255</v>
       </c>
-      <c r="D16" s="184" t="str">
+      <c r="D16" s="195" t="str">
         <v>净卖: -745.64万</v>
       </c>
       <c r="E16">
@@ -4989,40 +4989,40 @@
       <c r="H16">
         <v>-10</v>
       </c>
-      <c r="I16" s="194">
+      <c r="I16" s="189">
         <v>0</v>
       </c>
-      <c r="J16" s="191">
+      <c r="J16" s="192">
         <v>-10</v>
       </c>
-      <c r="K16" s="185">
+      <c r="K16" s="190">
         <v>-1</v>
       </c>
-      <c r="L16" s="186">
+      <c r="L16" s="183">
         <v>-10.9</v>
       </c>
-      <c r="M16" s="195">
+      <c r="M16" s="193">
         <v>-17.03</v>
       </c>
-      <c r="N16" s="187">
+      <c r="N16" s="184">
         <v>-11.34</v>
       </c>
-      <c r="O16" s="188">
+      <c r="O16" s="185">
         <v>-8.27</v>
       </c>
-      <c r="P16" s="183">
+      <c r="P16" s="186">
         <v>-9.76</v>
       </c>
-      <c r="Q16" s="192">
+      <c r="Q16" s="187">
         <v>-11.21</v>
       </c>
-      <c r="R16" s="189">
+      <c r="R16" s="191">
         <v>-12.68</v>
       </c>
-      <c r="S16" s="190">
+      <c r="S16" s="188">
         <v>-21.41</v>
       </c>
-      <c r="T16" s="193">
+      <c r="T16" s="194">
         <v>-38.91</v>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       <c r="C17" t="str">
         <v>601139</v>
       </c>
-      <c r="D17" s="205" t="str">
+      <c r="D17" s="201" t="str">
         <v>净卖: -3779.77万</v>
       </c>
       <c r="E17">
@@ -5051,28 +5051,28 @@
       <c r="H17">
         <v>1.68</v>
       </c>
-      <c r="I17" s="201">
+      <c r="I17" s="202">
         <v>8.25</v>
       </c>
-      <c r="J17" s="204">
+      <c r="J17" s="196">
         <v>0.41</v>
       </c>
-      <c r="K17" s="197">
+      <c r="K17" s="203">
         <v>-3.58</v>
       </c>
-      <c r="L17" s="198">
+      <c r="L17" s="197">
         <v>-3.03</v>
       </c>
-      <c r="M17" s="202">
+      <c r="M17" s="204">
         <v>-0.55</v>
       </c>
-      <c r="N17" s="203">
+      <c r="N17" s="198">
         <v>-1.79</v>
       </c>
-      <c r="O17" s="199">
+      <c r="O17" s="205">
         <v>-0.41</v>
       </c>
-      <c r="P17" s="200">
+      <c r="P17" s="199">
         <v>7.7</v>
       </c>
       <c r="Q17" s="206">
@@ -5081,10 +5081,10 @@
       <c r="R17" s="207">
         <v>3.03</v>
       </c>
-      <c r="S17" s="208">
+      <c r="S17" s="200">
         <v>0</v>
       </c>
-      <c r="T17" s="196">
+      <c r="T17" s="208">
         <v>-6.46</v>
       </c>
     </row>
@@ -5150,25 +5150,25 @@
       <c r="I19" s="214">
         <v>43.75</v>
       </c>
-      <c r="J19" s="209">
+      <c r="J19" s="215">
         <v>31.25</v>
       </c>
-      <c r="K19" s="219">
+      <c r="K19" s="220">
         <v>25</v>
       </c>
-      <c r="L19" s="215">
+      <c r="L19" s="210">
         <v>18.75</v>
       </c>
-      <c r="M19" s="216">
+      <c r="M19" s="209">
         <v>31.25</v>
       </c>
-      <c r="N19" s="217">
+      <c r="N19" s="212">
         <v>37.5</v>
       </c>
-      <c r="O19" s="220">
+      <c r="O19" s="216">
         <v>31.25</v>
       </c>
-      <c r="P19" s="210">
+      <c r="P19" s="217">
         <v>37.5</v>
       </c>
       <c r="Q19" s="211">
@@ -5177,7 +5177,7 @@
       <c r="R19" s="218">
         <v>37.5</v>
       </c>
-      <c r="S19" s="212">
+      <c r="S19" s="219">
         <v>31.25</v>
       </c>
       <c r="T19" s="213">
@@ -5195,37 +5195,37 @@
       <c r="F20" t="str"/>
       <c r="G20" t="str"/>
       <c r="H20" t="str"/>
-      <c r="I20" s="226">
+      <c r="I20" s="223">
         <v>3.11</v>
       </c>
-      <c r="J20" s="229">
+      <c r="J20" s="228">
         <v>-2.73</v>
       </c>
-      <c r="K20" s="230">
+      <c r="K20" s="224">
         <v>-4.91</v>
       </c>
-      <c r="L20" s="231">
+      <c r="L20" s="229">
         <v>-7.8</v>
       </c>
-      <c r="M20" s="223">
+      <c r="M20" s="225">
         <v>-5.55</v>
       </c>
-      <c r="N20" s="227">
+      <c r="N20" s="230">
         <v>-5.78</v>
       </c>
-      <c r="O20" s="232">
+      <c r="O20" s="231">
         <v>-6.29</v>
       </c>
-      <c r="P20" s="224">
+      <c r="P20" s="226">
         <v>-4.87</v>
       </c>
-      <c r="Q20" s="228">
+      <c r="Q20" s="227">
         <v>-5.25</v>
       </c>
-      <c r="R20" s="221">
+      <c r="R20" s="232">
         <v>-5.94</v>
       </c>
-      <c r="S20" s="225">
+      <c r="S20" s="221">
         <v>-6.59</v>
       </c>
       <c r="T20" s="222">

--- a/youzi/金田路/index.xlsx
+++ b/youzi/金田路/index.xlsx
@@ -39,19 +39,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,19 +117,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15361"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE77A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,37 +213,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
+        <fgColor rgb="FF1F8437"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,31 +225,733 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C78A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77882"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4DB665"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF24993F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15361"/>
+        <fgColor rgb="FF2AA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,19 +963,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBC73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,7 +1011,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,37 +1035,343 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,1129 +1383,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE77A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAE55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77882"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA2AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBC73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2AA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4DB665"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1377,43 +1413,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4106,7 +4106,7 @@
       <c r="C2" t="str">
         <v>603124</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="13" t="str">
         <v>净买: 3338.76万</v>
       </c>
       <c r="E2">
@@ -4121,41 +4121,41 @@
       <c r="H2">
         <v>526.19</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="1">
         <v>12.88</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="2">
         <v>-12.55</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="9">
         <v>-22.7</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="7">
         <v>-26.47</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="10">
         <v>-25.17</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="5">
         <v>-30.67</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="3">
         <v>-32.55</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="6">
         <v>-31.88</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="Q2" s="4">
         <v>-29.12</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="11">
         <v>-30.52</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="8">
         <v>-28.5</v>
       </c>
-      <c r="T2" s="8">
-        <v>87.91</v>
+      <c r="T2" s="12">
+        <v>85.98</v>
       </c>
     </row>
     <row r="3">
@@ -4183,41 +4183,41 @@
       <c r="H3">
         <v>-4.14</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="14">
         <v>-6.15</v>
       </c>
       <c r="J3" s="22">
         <v>-1.99</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="17">
         <v>-0.75</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="19">
         <v>3.41</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="23">
         <v>7.06</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="15">
         <v>9.39</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="16">
         <v>5.32</v>
       </c>
       <c r="P3" s="20">
         <v>4.24</v>
       </c>
-      <c r="Q3" s="25">
+      <c r="Q3" s="18">
         <v>4.98</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="24">
         <v>6.56</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="25">
         <v>4.73</v>
       </c>
-      <c r="T3" s="15">
-        <v>354.73</v>
+      <c r="T3" s="26">
+        <v>350.17</v>
       </c>
     </row>
     <row r="4">
@@ -4230,7 +4230,7 @@
       <c r="C4" t="str">
         <v>600418</v>
       </c>
-      <c r="D4" s="28" t="str">
+      <c r="D4" s="37" t="str">
         <v>净卖: -8419.55万</v>
       </c>
       <c r="E4">
@@ -4245,41 +4245,41 @@
       <c r="H4">
         <v>-0.78</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="38">
         <v>-6.97</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="28">
         <v>-8.32</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="30">
         <v>-7.89</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="39">
         <v>-7.79</v>
       </c>
       <c r="M4" s="33">
         <v>1.42</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="27">
         <v>3.29</v>
       </c>
-      <c r="O4" s="37">
+      <c r="O4" s="29">
         <v>10.45</v>
       </c>
-      <c r="P4" s="38">
+      <c r="P4" s="31">
         <v>15.53</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="34">
         <v>12.95</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="32">
         <v>13.61</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="35">
         <v>11.08</v>
       </c>
       <c r="T4" s="36">
-        <v>22.39</v>
+        <v>22.53</v>
       </c>
     </row>
     <row r="5">
@@ -4307,41 +4307,41 @@
       <c r="H5">
         <v>0.25</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="42">
         <v>-10</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="41">
         <v>-0.99</v>
       </c>
       <c r="K5" s="48">
         <v>-1.82</v>
       </c>
-      <c r="L5" s="41">
+      <c r="L5" s="49">
         <v>-10.66</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="44">
         <v>-12.81</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="50">
         <v>-10.33</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="51">
         <v>-9.92</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="45">
         <v>-11.24</v>
       </c>
-      <c r="Q5" s="51">
+      <c r="Q5" s="52">
         <v>-10.25</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="40">
         <v>-11.07</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="46">
         <v>-12.73</v>
       </c>
-      <c r="T5" s="40">
-        <v>-4.55</v>
+      <c r="T5" s="43">
+        <v>-2.31</v>
       </c>
     </row>
     <row r="6">
@@ -4354,7 +4354,7 @@
       <c r="C6" t="str">
         <v>001331</v>
       </c>
-      <c r="D6" s="59" t="str">
+      <c r="D6" s="56" t="str">
         <v>净买: 966.34万</v>
       </c>
       <c r="E6">
@@ -4369,41 +4369,41 @@
       <c r="H6">
         <v>10.01</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="61">
         <v>0</v>
       </c>
-      <c r="J6" s="60">
+      <c r="J6" s="64">
         <v>-9.55</v>
       </c>
-      <c r="K6" s="65">
+      <c r="K6" s="57">
         <v>-18.58</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="58">
         <v>-22.16</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="59">
         <v>-22.81</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="65">
         <v>-22.42</v>
       </c>
-      <c r="O6" s="62">
+      <c r="O6" s="53">
         <v>-22.29</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="54">
         <v>-22.03</v>
       </c>
       <c r="Q6" s="55">
         <v>-18.52</v>
       </c>
-      <c r="R6" s="56">
+      <c r="R6" s="60">
         <v>-16.83</v>
       </c>
-      <c r="S6" s="57">
+      <c r="S6" s="62">
         <v>-16.76</v>
       </c>
-      <c r="T6" s="58">
-        <v>231.12</v>
+      <c r="T6" s="63">
+        <v>232.62</v>
       </c>
     </row>
     <row r="7">
@@ -4416,7 +4416,7 @@
       <c r="C7" t="str">
         <v>605169</v>
       </c>
-      <c r="D7" s="70" t="str">
+      <c r="D7" s="77" t="str">
         <v>净卖: -1118.05万</v>
       </c>
       <c r="E7">
@@ -4431,41 +4431,41 @@
       <c r="H7">
         <v>-4.72</v>
       </c>
-      <c r="I7" s="74">
+      <c r="I7" s="78">
         <v>15.46</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="73">
         <v>12.98</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="74">
         <v>2.95</v>
       </c>
-      <c r="L7" s="75">
+      <c r="L7" s="66">
         <v>-4.72</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="75">
         <v>-3.13</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="67">
         <v>-5.78</v>
       </c>
-      <c r="O7" s="78">
+      <c r="O7" s="76">
         <v>-5.01</v>
       </c>
-      <c r="P7" s="73">
+      <c r="P7" s="69">
         <v>-6.43</v>
       </c>
-      <c r="Q7" s="66">
+      <c r="Q7" s="68">
         <v>-10.5</v>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="70">
         <v>-9.79</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="72">
         <v>-11.15</v>
       </c>
-      <c r="T7" s="69">
-        <v>-28.26</v>
+      <c r="T7" s="71">
+        <v>-27.32</v>
       </c>
     </row>
     <row r="8">
@@ -4478,7 +4478,7 @@
       <c r="C8" t="str">
         <v>836699</v>
       </c>
-      <c r="D8" s="89" t="str">
+      <c r="D8" s="85" t="str">
         <v>净卖: -801.39万</v>
       </c>
       <c r="E8">
@@ -4493,40 +4493,40 @@
       <c r="H8">
         <v>1.68</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="79">
         <v>27.86</v>
       </c>
-      <c r="J8" s="83">
+      <c r="J8" s="82">
         <v>25.31</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="86">
         <v>20.9</v>
       </c>
-      <c r="L8" s="81">
+      <c r="L8" s="80">
         <v>14.59</v>
       </c>
-      <c r="M8" s="90">
+      <c r="M8" s="83">
         <v>31.58</v>
       </c>
       <c r="N8" s="91">
         <v>29.44</v>
       </c>
-      <c r="O8" s="84">
+      <c r="O8" s="87">
         <v>22.64</v>
       </c>
-      <c r="P8" s="82">
+      <c r="P8" s="88">
         <v>24.9</v>
       </c>
-      <c r="Q8" s="79">
+      <c r="Q8" s="81">
         <v>20.99</v>
       </c>
-      <c r="R8" s="88">
+      <c r="R8" s="84">
         <v>18.14</v>
       </c>
-      <c r="S8" s="85">
+      <c r="S8" s="89">
         <v>36.74</v>
       </c>
-      <c r="T8" s="86">
+      <c r="T8" s="90">
         <v>30.08</v>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       <c r="C9" t="str">
         <v>301632</v>
       </c>
-      <c r="D9" s="104" t="str">
+      <c r="D9" s="96" t="str">
         <v>净买: 2340.61万</v>
       </c>
       <c r="E9">
@@ -4558,38 +4558,38 @@
       <c r="I9" s="92">
         <v>-13.93</v>
       </c>
-      <c r="J9" s="100">
+      <c r="J9" s="94">
         <v>-17.96</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="101">
         <v>-18.95</v>
       </c>
-      <c r="L9" s="101">
+      <c r="L9" s="102">
         <v>-17</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="103">
         <v>-21.23</v>
       </c>
-      <c r="N9" s="102">
+      <c r="N9" s="104">
         <v>-26.34</v>
       </c>
-      <c r="O9" s="96">
+      <c r="O9" s="93">
         <v>-26.39</v>
       </c>
-      <c r="P9" s="103">
+      <c r="P9" s="95">
         <v>-25.82</v>
       </c>
       <c r="Q9" s="97">
         <v>-28.19</v>
       </c>
-      <c r="R9" s="93">
+      <c r="R9" s="98">
         <v>-30.97</v>
       </c>
-      <c r="S9" s="98">
+      <c r="S9" s="99">
         <v>-30.82</v>
       </c>
-      <c r="T9" s="99">
-        <v>-53.45</v>
+      <c r="T9" s="100">
+        <v>-53.13</v>
       </c>
     </row>
     <row r="10">
@@ -4602,7 +4602,7 @@
       <c r="C10" t="str">
         <v>300948</v>
       </c>
-      <c r="D10" s="113" t="str">
+      <c r="D10" s="105" t="str">
         <v>净卖: -709.60万</v>
       </c>
       <c r="E10">
@@ -4617,41 +4617,41 @@
       <c r="H10">
         <v>2.78</v>
       </c>
-      <c r="I10" s="114">
+      <c r="I10" s="109">
         <v>16.75</v>
       </c>
-      <c r="J10" s="110">
+      <c r="J10" s="114">
         <v>1.59</v>
       </c>
-      <c r="K10" s="111">
+      <c r="K10" s="115">
         <v>0.16</v>
       </c>
-      <c r="L10" s="115">
+      <c r="L10" s="110">
         <v>-2.23</v>
       </c>
-      <c r="M10" s="116">
+      <c r="M10" s="106">
         <v>5.35</v>
       </c>
-      <c r="N10" s="106">
+      <c r="N10" s="111">
         <v>8.32</v>
       </c>
       <c r="O10" s="112">
         <v>9.38</v>
       </c>
-      <c r="P10" s="117">
+      <c r="P10" s="113">
         <v>10.44</v>
       </c>
       <c r="Q10" s="107">
         <v>8.64</v>
       </c>
-      <c r="R10" s="105">
+      <c r="R10" s="108">
         <v>4.13</v>
       </c>
-      <c r="S10" s="108">
+      <c r="S10" s="116">
         <v>3.34</v>
       </c>
-      <c r="T10" s="109">
-        <v>2.28</v>
+      <c r="T10" s="117">
+        <v>6.78</v>
       </c>
     </row>
     <row r="11">
@@ -4664,7 +4664,7 @@
       <c r="C11" t="str">
         <v>000069</v>
       </c>
-      <c r="D11" s="120" t="str">
+      <c r="D11" s="121" t="str">
         <v>净买: 3152.70万</v>
       </c>
       <c r="E11">
@@ -4679,41 +4679,41 @@
       <c r="H11">
         <v>1.88</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="120">
         <v>8.12</v>
       </c>
-      <c r="J11" s="125">
+      <c r="J11" s="122">
         <v>3.69</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="123">
         <v>4.06</v>
       </c>
-      <c r="L11" s="121">
+      <c r="L11" s="124">
         <v>2.95</v>
       </c>
-      <c r="M11" s="118">
+      <c r="M11" s="129">
         <v>4.8</v>
       </c>
-      <c r="N11" s="122">
+      <c r="N11" s="125">
         <v>0.37</v>
       </c>
-      <c r="O11" s="123">
+      <c r="O11" s="126">
         <v>-2.95</v>
       </c>
-      <c r="P11" s="124">
+      <c r="P11" s="127">
         <v>0</v>
       </c>
-      <c r="Q11" s="126">
+      <c r="Q11" s="130">
         <v>-1.11</v>
       </c>
-      <c r="R11" s="127">
+      <c r="R11" s="119">
         <v>-1.85</v>
       </c>
-      <c r="S11" s="128">
+      <c r="S11" s="118">
         <v>0</v>
       </c>
-      <c r="T11" s="129">
-        <v>-17.71</v>
+      <c r="T11" s="128">
+        <v>-18.08</v>
       </c>
     </row>
     <row r="12">
@@ -4726,7 +4726,7 @@
       <c r="C12" t="str">
         <v>002242</v>
       </c>
-      <c r="D12" s="139" t="str">
+      <c r="D12" s="135" t="str">
         <v>净卖: -1077.90万</v>
       </c>
       <c r="E12">
@@ -4741,41 +4741,41 @@
       <c r="H12">
         <v>10.04</v>
       </c>
-      <c r="I12" s="135">
+      <c r="I12" s="136">
         <v>0</v>
       </c>
-      <c r="J12" s="140">
+      <c r="J12" s="132">
         <v>-4.93</v>
       </c>
       <c r="K12" s="133">
         <v>-3.04</v>
       </c>
-      <c r="L12" s="143">
+      <c r="L12" s="137">
         <v>-11.42</v>
       </c>
-      <c r="M12" s="141">
+      <c r="M12" s="138">
         <v>-11.83</v>
       </c>
-      <c r="N12" s="134">
+      <c r="N12" s="142">
         <v>-15.61</v>
       </c>
-      <c r="O12" s="142">
+      <c r="O12" s="140">
         <v>-15.12</v>
       </c>
-      <c r="P12" s="136">
+      <c r="P12" s="134">
         <v>-14.71</v>
       </c>
-      <c r="Q12" s="137">
+      <c r="Q12" s="143">
         <v>-15.37</v>
       </c>
-      <c r="R12" s="138">
+      <c r="R12" s="139">
         <v>-14.13</v>
       </c>
       <c r="S12" s="131">
         <v>-14.13</v>
       </c>
-      <c r="T12" s="132">
-        <v>-15.94</v>
+      <c r="T12" s="141">
+        <v>-7.56</v>
       </c>
     </row>
     <row r="13">
@@ -4788,7 +4788,7 @@
       <c r="C13" t="str">
         <v>603877</v>
       </c>
-      <c r="D13" s="156" t="str">
+      <c r="D13" s="149" t="str">
         <v>净卖: -596.03万</v>
       </c>
       <c r="E13">
@@ -4803,10 +4803,10 @@
       <c r="H13">
         <v>3.85</v>
       </c>
-      <c r="I13" s="152">
+      <c r="I13" s="147">
         <v>5.94</v>
       </c>
-      <c r="J13" s="147">
+      <c r="J13" s="144">
         <v>0</v>
       </c>
       <c r="K13" s="150">
@@ -4815,29 +4815,29 @@
       <c r="L13" s="153">
         <v>-4.29</v>
       </c>
-      <c r="M13" s="148">
+      <c r="M13" s="151">
         <v>-4.94</v>
       </c>
       <c r="N13" s="154">
         <v>-5</v>
       </c>
-      <c r="O13" s="149">
+      <c r="O13" s="155">
         <v>-7.41</v>
       </c>
-      <c r="P13" s="144">
+      <c r="P13" s="156">
         <v>-3.76</v>
       </c>
-      <c r="Q13" s="155">
+      <c r="Q13" s="145">
         <v>-4.12</v>
       </c>
-      <c r="R13" s="145">
+      <c r="R13" s="146">
         <v>-4.24</v>
       </c>
-      <c r="S13" s="146">
+      <c r="S13" s="148">
         <v>-5.88</v>
       </c>
-      <c r="T13" s="151">
-        <v>-13.41</v>
+      <c r="T13" s="152">
+        <v>-11.88</v>
       </c>
     </row>
     <row r="14">
@@ -4850,7 +4850,7 @@
       <c r="C14" t="str">
         <v>603216</v>
       </c>
-      <c r="D14" s="157" t="str">
+      <c r="D14" s="162" t="str">
         <v>净买: 462.51万</v>
       </c>
       <c r="E14">
@@ -4865,41 +4865,41 @@
       <c r="H14">
         <v>-6.54</v>
       </c>
-      <c r="I14" s="168">
+      <c r="I14" s="163">
         <v>-3.72</v>
       </c>
-      <c r="J14" s="166">
+      <c r="J14" s="169">
         <v>-9.38</v>
       </c>
       <c r="K14" s="164">
         <v>-2.23</v>
       </c>
-      <c r="L14" s="158">
+      <c r="L14" s="157">
         <v>-4.26</v>
       </c>
-      <c r="M14" s="159">
+      <c r="M14" s="158">
         <v>-0.51</v>
       </c>
-      <c r="N14" s="160">
+      <c r="N14" s="167">
         <v>9.31</v>
       </c>
-      <c r="O14" s="167">
+      <c r="O14" s="165">
         <v>5.63</v>
       </c>
-      <c r="P14" s="161">
+      <c r="P14" s="159">
         <v>5.63</v>
       </c>
-      <c r="Q14" s="162">
+      <c r="Q14" s="160">
         <v>11.51</v>
       </c>
-      <c r="R14" s="163">
+      <c r="R14" s="166">
         <v>11.89</v>
       </c>
-      <c r="S14" s="169">
+      <c r="S14" s="168">
         <v>2.92</v>
       </c>
-      <c r="T14" s="165">
-        <v>-3.69</v>
+      <c r="T14" s="161">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="15">
@@ -4912,7 +4912,7 @@
       <c r="C15" t="str">
         <v>002589</v>
       </c>
-      <c r="D15" s="174" t="str">
+      <c r="D15" s="177" t="str">
         <v>净买: 1428.73万</v>
       </c>
       <c r="E15">
@@ -4927,40 +4927,40 @@
       <c r="H15">
         <v>-5.54</v>
       </c>
-      <c r="I15" s="173">
+      <c r="I15" s="171">
         <v>-4.74</v>
       </c>
-      <c r="J15" s="178">
+      <c r="J15" s="182">
         <v>-11.96</v>
       </c>
-      <c r="K15" s="175">
+      <c r="K15" s="172">
         <v>-19.86</v>
       </c>
-      <c r="L15" s="182">
+      <c r="L15" s="178">
         <v>-20.77</v>
       </c>
-      <c r="M15" s="170">
+      <c r="M15" s="173">
         <v>-18.96</v>
       </c>
-      <c r="N15" s="176">
+      <c r="N15" s="170">
         <v>-23.25</v>
       </c>
-      <c r="O15" s="179">
+      <c r="O15" s="174">
         <v>-23.7</v>
       </c>
-      <c r="P15" s="177">
+      <c r="P15" s="179">
         <v>-20.77</v>
       </c>
       <c r="Q15" s="180">
         <v>-19.86</v>
       </c>
-      <c r="R15" s="171">
+      <c r="R15" s="181">
         <v>-20.32</v>
       </c>
-      <c r="S15" s="181">
+      <c r="S15" s="175">
         <v>-22.8</v>
       </c>
-      <c r="T15" s="172">
+      <c r="T15" s="176">
         <v>-22.57</v>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       <c r="C16" t="str">
         <v>605255</v>
       </c>
-      <c r="D16" s="195" t="str">
+      <c r="D16" s="194" t="str">
         <v>净卖: -745.64万</v>
       </c>
       <c r="E16">
@@ -4989,41 +4989,41 @@
       <c r="H16">
         <v>-10</v>
       </c>
-      <c r="I16" s="189">
+      <c r="I16" s="191">
         <v>0</v>
       </c>
       <c r="J16" s="192">
         <v>-10</v>
       </c>
-      <c r="K16" s="190">
+      <c r="K16" s="188">
         <v>-1</v>
       </c>
-      <c r="L16" s="183">
+      <c r="L16" s="193">
         <v>-10.9</v>
       </c>
-      <c r="M16" s="193">
+      <c r="M16" s="195">
         <v>-17.03</v>
       </c>
-      <c r="N16" s="184">
+      <c r="N16" s="183">
         <v>-11.34</v>
       </c>
-      <c r="O16" s="185">
+      <c r="O16" s="184">
         <v>-8.27</v>
       </c>
-      <c r="P16" s="186">
+      <c r="P16" s="189">
         <v>-9.76</v>
       </c>
-      <c r="Q16" s="187">
+      <c r="Q16" s="185">
         <v>-11.21</v>
       </c>
-      <c r="R16" s="191">
+      <c r="R16" s="186">
         <v>-12.68</v>
       </c>
-      <c r="S16" s="188">
+      <c r="S16" s="187">
         <v>-21.41</v>
       </c>
-      <c r="T16" s="194">
-        <v>-38.91</v>
+      <c r="T16" s="190">
+        <v>-40.63</v>
       </c>
     </row>
     <row r="17">
@@ -5036,7 +5036,7 @@
       <c r="C17" t="str">
         <v>601139</v>
       </c>
-      <c r="D17" s="201" t="str">
+      <c r="D17" s="203" t="str">
         <v>净卖: -3779.77万</v>
       </c>
       <c r="E17">
@@ -5051,41 +5051,41 @@
       <c r="H17">
         <v>1.68</v>
       </c>
-      <c r="I17" s="202">
+      <c r="I17" s="197">
         <v>8.25</v>
       </c>
-      <c r="J17" s="196">
+      <c r="J17" s="206">
         <v>0.41</v>
       </c>
-      <c r="K17" s="203">
+      <c r="K17" s="205">
         <v>-3.58</v>
       </c>
-      <c r="L17" s="197">
+      <c r="L17" s="198">
         <v>-3.03</v>
       </c>
-      <c r="M17" s="204">
+      <c r="M17" s="207">
         <v>-0.55</v>
       </c>
-      <c r="N17" s="198">
+      <c r="N17" s="199">
         <v>-1.79</v>
       </c>
-      <c r="O17" s="205">
+      <c r="O17" s="208">
         <v>-0.41</v>
       </c>
-      <c r="P17" s="199">
+      <c r="P17" s="204">
         <v>7.7</v>
       </c>
-      <c r="Q17" s="206">
+      <c r="Q17" s="196">
         <v>5.23</v>
       </c>
-      <c r="R17" s="207">
+      <c r="R17" s="200">
         <v>3.03</v>
       </c>
-      <c r="S17" s="200">
+      <c r="S17" s="201">
         <v>0</v>
       </c>
-      <c r="T17" s="208">
-        <v>-6.46</v>
+      <c r="T17" s="202">
+        <v>-5.64</v>
       </c>
     </row>
     <row r="18">
@@ -5147,40 +5147,40 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="214">
+      <c r="I19" s="215">
         <v>43.75</v>
       </c>
-      <c r="J19" s="215">
+      <c r="J19" s="216">
         <v>31.25</v>
       </c>
-      <c r="K19" s="220">
+      <c r="K19" s="218">
         <v>25</v>
       </c>
-      <c r="L19" s="210">
+      <c r="L19" s="217">
         <v>18.75</v>
       </c>
-      <c r="M19" s="209">
+      <c r="M19" s="212">
         <v>31.25</v>
       </c>
-      <c r="N19" s="212">
+      <c r="N19" s="213">
         <v>37.5</v>
       </c>
-      <c r="O19" s="216">
+      <c r="O19" s="220">
         <v>31.25</v>
       </c>
-      <c r="P19" s="217">
+      <c r="P19" s="209">
         <v>37.5</v>
       </c>
-      <c r="Q19" s="211">
+      <c r="Q19" s="210">
         <v>37.5</v>
       </c>
-      <c r="R19" s="218">
+      <c r="R19" s="219">
         <v>37.5</v>
       </c>
-      <c r="S19" s="219">
+      <c r="S19" s="211">
         <v>31.25</v>
       </c>
-      <c r="T19" s="213">
+      <c r="T19" s="214">
         <v>37.5</v>
       </c>
     </row>
@@ -5195,25 +5195,25 @@
       <c r="F20" t="str"/>
       <c r="G20" t="str"/>
       <c r="H20" t="str"/>
-      <c r="I20" s="223">
+      <c r="I20" s="229">
         <v>3.11</v>
       </c>
-      <c r="J20" s="228">
+      <c r="J20" s="230">
         <v>-2.73</v>
       </c>
-      <c r="K20" s="224">
+      <c r="K20" s="221">
         <v>-4.91</v>
       </c>
-      <c r="L20" s="229">
+      <c r="L20" s="231">
         <v>-7.8</v>
       </c>
-      <c r="M20" s="225">
+      <c r="M20" s="228">
         <v>-5.55</v>
       </c>
-      <c r="N20" s="230">
+      <c r="N20" s="225">
         <v>-5.78</v>
       </c>
-      <c r="O20" s="231">
+      <c r="O20" s="232">
         <v>-6.29</v>
       </c>
       <c r="P20" s="226">
@@ -5222,14 +5222,14 @@
       <c r="Q20" s="227">
         <v>-5.25</v>
       </c>
-      <c r="R20" s="232">
+      <c r="R20" s="222">
         <v>-5.94</v>
       </c>
-      <c r="S20" s="221">
+      <c r="S20" s="223">
         <v>-6.59</v>
       </c>
-      <c r="T20" s="222">
-        <v>32.72</v>
+      <c r="T20" s="224">
+        <v>33.58</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/金田路/index.xlsx
+++ b/youzi/金田路/index.xlsx
@@ -39,31 +39,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,31 +105,877 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15361"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C78A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77882"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBC73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4DB665"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF24993F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
+        <fgColor rgb="FF2AA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,13 +987,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15361"/>
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,1255 +1137,283 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77882"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4DB665"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2AA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBC73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4106,7 +4106,7 @@
       <c r="C2" t="str">
         <v>603124</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="4" t="str">
         <v>净买: 3338.76万</v>
       </c>
       <c r="E2">
@@ -4121,41 +4121,41 @@
       <c r="H2">
         <v>526.19</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="11">
         <v>12.88</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="5">
         <v>-12.55</v>
       </c>
       <c r="K2" s="9">
         <v>-22.7</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="12">
         <v>-26.47</v>
       </c>
       <c r="M2" s="10">
         <v>-25.17</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="6">
         <v>-30.67</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="2">
         <v>-32.55</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="7">
         <v>-31.88</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="8">
         <v>-29.12</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="13">
         <v>-30.52</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="1">
         <v>-28.5</v>
       </c>
-      <c r="T2" s="12">
-        <v>85.98</v>
+      <c r="T2" s="3">
+        <v>87.35</v>
       </c>
     </row>
     <row r="3">
@@ -4168,7 +4168,7 @@
       <c r="C3" t="str">
         <v>605298</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="24" t="str">
         <v>净卖: -183.82万</v>
       </c>
       <c r="E3">
@@ -4186,38 +4186,38 @@
       <c r="I3" s="14">
         <v>-6.15</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="15">
         <v>-1.99</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="16">
         <v>-0.75</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="25">
         <v>3.41</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="21">
         <v>7.06</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N3" s="17">
         <v>9.39</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="18">
         <v>5.32</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="19">
         <v>4.24</v>
       </c>
-      <c r="Q3" s="18">
+      <c r="Q3" s="22">
         <v>4.98</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="20">
         <v>6.56</v>
       </c>
-      <c r="S3" s="25">
+      <c r="S3" s="26">
         <v>4.73</v>
       </c>
-      <c r="T3" s="26">
-        <v>350.17</v>
+      <c r="T3" s="23">
+        <v>395.18</v>
       </c>
     </row>
     <row r="4">
@@ -4230,7 +4230,7 @@
       <c r="C4" t="str">
         <v>600418</v>
       </c>
-      <c r="D4" s="37" t="str">
+      <c r="D4" s="35" t="str">
         <v>净卖: -8419.55万</v>
       </c>
       <c r="E4">
@@ -4245,41 +4245,41 @@
       <c r="H4">
         <v>-0.78</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="30">
         <v>-6.97</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="31">
         <v>-8.32</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="32">
         <v>-7.89</v>
       </c>
-      <c r="L4" s="39">
+      <c r="L4" s="34">
         <v>-7.79</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="36">
         <v>1.42</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="38">
         <v>3.29</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="39">
         <v>10.45</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="27">
         <v>15.53</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="37">
         <v>12.95</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="33">
         <v>13.61</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="28">
         <v>11.08</v>
       </c>
-      <c r="T4" s="36">
-        <v>22.53</v>
+      <c r="T4" s="29">
+        <v>20.26</v>
       </c>
     </row>
     <row r="5">
@@ -4292,7 +4292,7 @@
       <c r="C5" t="str">
         <v>002856</v>
       </c>
-      <c r="D5" s="47" t="str">
+      <c r="D5" s="41" t="str">
         <v>净买: 382.36万</v>
       </c>
       <c r="E5">
@@ -4307,19 +4307,19 @@
       <c r="H5">
         <v>0.25</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="47">
         <v>-10</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="42">
         <v>-0.99</v>
       </c>
       <c r="K5" s="48">
         <v>-1.82</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="43">
         <v>-10.66</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="49">
         <v>-12.81</v>
       </c>
       <c r="N5" s="50">
@@ -4328,20 +4328,20 @@
       <c r="O5" s="51">
         <v>-9.92</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="52">
         <v>-11.24</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="44">
         <v>-10.25</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="45">
         <v>-11.07</v>
       </c>
       <c r="S5" s="46">
         <v>-12.73</v>
       </c>
-      <c r="T5" s="43">
-        <v>-2.31</v>
+      <c r="T5" s="40">
+        <v>3.72</v>
       </c>
     </row>
     <row r="6">
@@ -4369,41 +4369,41 @@
       <c r="H6">
         <v>10.01</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="54">
         <v>0</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="61">
         <v>-9.55</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="64">
         <v>-18.58</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="62">
         <v>-22.16</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="57">
         <v>-22.81</v>
       </c>
       <c r="N6" s="65">
         <v>-22.42</v>
       </c>
-      <c r="O6" s="53">
+      <c r="O6" s="63">
         <v>-22.29</v>
       </c>
-      <c r="P6" s="54">
+      <c r="P6" s="58">
         <v>-22.03</v>
       </c>
-      <c r="Q6" s="55">
+      <c r="Q6" s="53">
         <v>-18.52</v>
       </c>
-      <c r="R6" s="60">
+      <c r="R6" s="55">
         <v>-16.83</v>
       </c>
-      <c r="S6" s="62">
+      <c r="S6" s="59">
         <v>-16.76</v>
       </c>
-      <c r="T6" s="63">
-        <v>232.62</v>
+      <c r="T6" s="60">
+        <v>231.51</v>
       </c>
     </row>
     <row r="7">
@@ -4416,7 +4416,7 @@
       <c r="C7" t="str">
         <v>605169</v>
       </c>
-      <c r="D7" s="77" t="str">
+      <c r="D7" s="71" t="str">
         <v>净卖: -1118.05万</v>
       </c>
       <c r="E7">
@@ -4431,41 +4431,41 @@
       <c r="H7">
         <v>-4.72</v>
       </c>
-      <c r="I7" s="78">
+      <c r="I7" s="77">
         <v>15.46</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="78">
         <v>12.98</v>
       </c>
-      <c r="K7" s="74">
+      <c r="K7" s="66">
         <v>2.95</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="68">
         <v>-4.72</v>
       </c>
-      <c r="M7" s="75">
+      <c r="M7" s="67">
         <v>-3.13</v>
       </c>
-      <c r="N7" s="67">
+      <c r="N7" s="72">
         <v>-5.78</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="73">
         <v>-5.01</v>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="74">
         <v>-6.43</v>
       </c>
-      <c r="Q7" s="68">
+      <c r="Q7" s="75">
         <v>-10.5</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="76">
         <v>-9.79</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="69">
         <v>-11.15</v>
       </c>
-      <c r="T7" s="71">
-        <v>-27.32</v>
+      <c r="T7" s="70">
+        <v>-25.66</v>
       </c>
     </row>
     <row r="8">
@@ -4478,7 +4478,7 @@
       <c r="C8" t="str">
         <v>836699</v>
       </c>
-      <c r="D8" s="85" t="str">
+      <c r="D8" s="87" t="str">
         <v>净卖: -801.39万</v>
       </c>
       <c r="E8">
@@ -4493,40 +4493,40 @@
       <c r="H8">
         <v>1.68</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="84">
         <v>27.86</v>
       </c>
-      <c r="J8" s="82">
+      <c r="J8" s="90">
         <v>25.31</v>
       </c>
-      <c r="K8" s="86">
+      <c r="K8" s="88">
         <v>20.9</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="91">
         <v>14.59</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="79">
         <v>31.58</v>
       </c>
-      <c r="N8" s="91">
+      <c r="N8" s="89">
         <v>29.44</v>
       </c>
-      <c r="O8" s="87">
+      <c r="O8" s="81">
         <v>22.64</v>
       </c>
-      <c r="P8" s="88">
+      <c r="P8" s="82">
         <v>24.9</v>
       </c>
-      <c r="Q8" s="81">
+      <c r="Q8" s="85">
         <v>20.99</v>
       </c>
-      <c r="R8" s="84">
+      <c r="R8" s="86">
         <v>18.14</v>
       </c>
-      <c r="S8" s="89">
+      <c r="S8" s="80">
         <v>36.74</v>
       </c>
-      <c r="T8" s="90">
+      <c r="T8" s="83">
         <v>30.08</v>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       <c r="C9" t="str">
         <v>301632</v>
       </c>
-      <c r="D9" s="96" t="str">
+      <c r="D9" s="94" t="str">
         <v>净买: 2340.61万</v>
       </c>
       <c r="E9">
@@ -4555,41 +4555,41 @@
       <c r="H9">
         <v>2.77</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="95">
         <v>-13.93</v>
       </c>
-      <c r="J9" s="94">
+      <c r="J9" s="100">
         <v>-17.96</v>
       </c>
-      <c r="K9" s="101">
+      <c r="K9" s="103">
         <v>-18.95</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="96">
         <v>-17</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="97">
         <v>-21.23</v>
       </c>
-      <c r="N9" s="104">
+      <c r="N9" s="101">
         <v>-26.34</v>
       </c>
-      <c r="O9" s="93">
+      <c r="O9" s="102">
         <v>-26.39</v>
       </c>
-      <c r="P9" s="95">
+      <c r="P9" s="104">
         <v>-25.82</v>
       </c>
-      <c r="Q9" s="97">
+      <c r="Q9" s="98">
         <v>-28.19</v>
       </c>
-      <c r="R9" s="98">
+      <c r="R9" s="99">
         <v>-30.97</v>
       </c>
-      <c r="S9" s="99">
+      <c r="S9" s="92">
         <v>-30.82</v>
       </c>
-      <c r="T9" s="100">
-        <v>-53.13</v>
+      <c r="T9" s="93">
+        <v>-53.43</v>
       </c>
     </row>
     <row r="10">
@@ -4617,41 +4617,41 @@
       <c r="H10">
         <v>2.78</v>
       </c>
-      <c r="I10" s="109">
+      <c r="I10" s="106">
         <v>16.75</v>
       </c>
-      <c r="J10" s="114">
+      <c r="J10" s="117">
         <v>1.59</v>
       </c>
-      <c r="K10" s="115">
+      <c r="K10" s="110">
         <v>0.16</v>
       </c>
-      <c r="L10" s="110">
+      <c r="L10" s="111">
         <v>-2.23</v>
       </c>
-      <c r="M10" s="106">
+      <c r="M10" s="107">
         <v>5.35</v>
       </c>
-      <c r="N10" s="111">
+      <c r="N10" s="112">
         <v>8.32</v>
       </c>
-      <c r="O10" s="112">
+      <c r="O10" s="108">
         <v>9.38</v>
       </c>
-      <c r="P10" s="113">
+      <c r="P10" s="109">
         <v>10.44</v>
       </c>
-      <c r="Q10" s="107">
+      <c r="Q10" s="115">
         <v>8.64</v>
       </c>
-      <c r="R10" s="108">
+      <c r="R10" s="113">
         <v>4.13</v>
       </c>
-      <c r="S10" s="116">
+      <c r="S10" s="114">
         <v>3.34</v>
       </c>
-      <c r="T10" s="117">
-        <v>6.78</v>
+      <c r="T10" s="116">
+        <v>7.31</v>
       </c>
     </row>
     <row r="11">
@@ -4664,7 +4664,7 @@
       <c r="C11" t="str">
         <v>000069</v>
       </c>
-      <c r="D11" s="121" t="str">
+      <c r="D11" s="130" t="str">
         <v>净买: 3152.70万</v>
       </c>
       <c r="E11">
@@ -4679,41 +4679,41 @@
       <c r="H11">
         <v>1.88</v>
       </c>
-      <c r="I11" s="120">
+      <c r="I11" s="124">
         <v>8.12</v>
       </c>
-      <c r="J11" s="122">
+      <c r="J11" s="121">
         <v>3.69</v>
       </c>
-      <c r="K11" s="123">
+      <c r="K11" s="125">
         <v>4.06</v>
       </c>
-      <c r="L11" s="124">
+      <c r="L11" s="126">
         <v>2.95</v>
       </c>
-      <c r="M11" s="129">
+      <c r="M11" s="118">
         <v>4.8</v>
       </c>
-      <c r="N11" s="125">
+      <c r="N11" s="122">
         <v>0.37</v>
       </c>
-      <c r="O11" s="126">
+      <c r="O11" s="127">
         <v>-2.95</v>
       </c>
-      <c r="P11" s="127">
+      <c r="P11" s="123">
         <v>0</v>
       </c>
-      <c r="Q11" s="130">
+      <c r="Q11" s="128">
         <v>-1.11</v>
       </c>
-      <c r="R11" s="119">
+      <c r="R11" s="129">
         <v>-1.85</v>
       </c>
-      <c r="S11" s="118">
+      <c r="S11" s="119">
         <v>0</v>
       </c>
-      <c r="T11" s="128">
-        <v>-18.08</v>
+      <c r="T11" s="120">
+        <v>-18.82</v>
       </c>
     </row>
     <row r="12">
@@ -4726,7 +4726,7 @@
       <c r="C12" t="str">
         <v>002242</v>
       </c>
-      <c r="D12" s="135" t="str">
+      <c r="D12" s="134" t="str">
         <v>净卖: -1077.90万</v>
       </c>
       <c r="E12">
@@ -4741,41 +4741,41 @@
       <c r="H12">
         <v>10.04</v>
       </c>
-      <c r="I12" s="136">
+      <c r="I12" s="140">
         <v>0</v>
       </c>
-      <c r="J12" s="132">
+      <c r="J12" s="141">
         <v>-4.93</v>
       </c>
-      <c r="K12" s="133">
+      <c r="K12" s="139">
         <v>-3.04</v>
       </c>
-      <c r="L12" s="137">
+      <c r="L12" s="135">
         <v>-11.42</v>
       </c>
-      <c r="M12" s="138">
+      <c r="M12" s="142">
         <v>-11.83</v>
       </c>
-      <c r="N12" s="142">
+      <c r="N12" s="136">
         <v>-15.61</v>
       </c>
-      <c r="O12" s="140">
+      <c r="O12" s="131">
         <v>-15.12</v>
       </c>
-      <c r="P12" s="134">
+      <c r="P12" s="137">
         <v>-14.71</v>
       </c>
       <c r="Q12" s="143">
         <v>-15.37</v>
       </c>
-      <c r="R12" s="139">
+      <c r="R12" s="132">
         <v>-14.13</v>
       </c>
-      <c r="S12" s="131">
+      <c r="S12" s="138">
         <v>-14.13</v>
       </c>
-      <c r="T12" s="141">
-        <v>-7.56</v>
+      <c r="T12" s="133">
+        <v>-12.16</v>
       </c>
     </row>
     <row r="13">
@@ -4788,7 +4788,7 @@
       <c r="C13" t="str">
         <v>603877</v>
       </c>
-      <c r="D13" s="149" t="str">
+      <c r="D13" s="152" t="str">
         <v>净卖: -596.03万</v>
       </c>
       <c r="E13">
@@ -4806,38 +4806,38 @@
       <c r="I13" s="147">
         <v>5.94</v>
       </c>
-      <c r="J13" s="144">
+      <c r="J13" s="148">
         <v>0</v>
       </c>
-      <c r="K13" s="150">
+      <c r="K13" s="153">
         <v>-6.18</v>
       </c>
-      <c r="L13" s="153">
+      <c r="L13" s="151">
         <v>-4.29</v>
       </c>
-      <c r="M13" s="151">
+      <c r="M13" s="154">
         <v>-4.94</v>
       </c>
-      <c r="N13" s="154">
+      <c r="N13" s="155">
         <v>-5</v>
       </c>
-      <c r="O13" s="155">
+      <c r="O13" s="156">
         <v>-7.41</v>
       </c>
-      <c r="P13" s="156">
+      <c r="P13" s="144">
         <v>-3.76</v>
       </c>
       <c r="Q13" s="145">
         <v>-4.12</v>
       </c>
-      <c r="R13" s="146">
+      <c r="R13" s="149">
         <v>-4.24</v>
       </c>
-      <c r="S13" s="148">
+      <c r="S13" s="146">
         <v>-5.88</v>
       </c>
-      <c r="T13" s="152">
-        <v>-11.88</v>
+      <c r="T13" s="150">
+        <v>-11.24</v>
       </c>
     </row>
     <row r="14">
@@ -4850,7 +4850,7 @@
       <c r="C14" t="str">
         <v>603216</v>
       </c>
-      <c r="D14" s="162" t="str">
+      <c r="D14" s="158" t="str">
         <v>净买: 462.51万</v>
       </c>
       <c r="E14">
@@ -4865,41 +4865,41 @@
       <c r="H14">
         <v>-6.54</v>
       </c>
-      <c r="I14" s="163">
+      <c r="I14" s="160">
         <v>-3.72</v>
       </c>
-      <c r="J14" s="169">
+      <c r="J14" s="161">
         <v>-9.38</v>
       </c>
-      <c r="K14" s="164">
+      <c r="K14" s="168">
         <v>-2.23</v>
       </c>
-      <c r="L14" s="157">
+      <c r="L14" s="169">
         <v>-4.26</v>
       </c>
-      <c r="M14" s="158">
+      <c r="M14" s="159">
         <v>-0.51</v>
       </c>
-      <c r="N14" s="167">
+      <c r="N14" s="157">
         <v>9.31</v>
       </c>
-      <c r="O14" s="165">
+      <c r="O14" s="163">
         <v>5.63</v>
       </c>
-      <c r="P14" s="159">
+      <c r="P14" s="164">
         <v>5.63</v>
       </c>
-      <c r="Q14" s="160">
+      <c r="Q14" s="165">
         <v>11.51</v>
       </c>
       <c r="R14" s="166">
         <v>11.89</v>
       </c>
-      <c r="S14" s="168">
+      <c r="S14" s="167">
         <v>2.92</v>
       </c>
-      <c r="T14" s="161">
-        <v>-1.75</v>
+      <c r="T14" s="162">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="15">
@@ -4912,7 +4912,7 @@
       <c r="C15" t="str">
         <v>002589</v>
       </c>
-      <c r="D15" s="177" t="str">
+      <c r="D15" s="180" t="str">
         <v>净买: 1428.73万</v>
       </c>
       <c r="E15">
@@ -4927,41 +4927,41 @@
       <c r="H15">
         <v>-5.54</v>
       </c>
-      <c r="I15" s="171">
+      <c r="I15" s="174">
         <v>-4.74</v>
       </c>
-      <c r="J15" s="182">
+      <c r="J15" s="171">
         <v>-11.96</v>
       </c>
-      <c r="K15" s="172">
+      <c r="K15" s="175">
         <v>-19.86</v>
       </c>
       <c r="L15" s="178">
         <v>-20.77</v>
       </c>
-      <c r="M15" s="173">
+      <c r="M15" s="181">
         <v>-18.96</v>
       </c>
-      <c r="N15" s="170">
+      <c r="N15" s="176">
         <v>-23.25</v>
       </c>
-      <c r="O15" s="174">
+      <c r="O15" s="172">
         <v>-23.7</v>
       </c>
       <c r="P15" s="179">
         <v>-20.77</v>
       </c>
-      <c r="Q15" s="180">
+      <c r="Q15" s="182">
         <v>-19.86</v>
       </c>
-      <c r="R15" s="181">
+      <c r="R15" s="170">
         <v>-20.32</v>
       </c>
-      <c r="S15" s="175">
+      <c r="S15" s="173">
         <v>-22.8</v>
       </c>
-      <c r="T15" s="176">
-        <v>-22.57</v>
+      <c r="T15" s="177">
+        <v>-24.38</v>
       </c>
     </row>
     <row r="16">
@@ -4974,7 +4974,7 @@
       <c r="C16" t="str">
         <v>605255</v>
       </c>
-      <c r="D16" s="194" t="str">
+      <c r="D16" s="183" t="str">
         <v>净卖: -745.64万</v>
       </c>
       <c r="E16">
@@ -4989,41 +4989,41 @@
       <c r="H16">
         <v>-10</v>
       </c>
-      <c r="I16" s="191">
+      <c r="I16" s="186">
         <v>0</v>
       </c>
-      <c r="J16" s="192">
+      <c r="J16" s="187">
         <v>-10</v>
       </c>
-      <c r="K16" s="188">
+      <c r="K16" s="193">
         <v>-1</v>
       </c>
-      <c r="L16" s="193">
+      <c r="L16" s="189">
         <v>-10.9</v>
       </c>
-      <c r="M16" s="195">
+      <c r="M16" s="190">
         <v>-17.03</v>
       </c>
-      <c r="N16" s="183">
+      <c r="N16" s="191">
         <v>-11.34</v>
       </c>
-      <c r="O16" s="184">
+      <c r="O16" s="188">
         <v>-8.27</v>
       </c>
-      <c r="P16" s="189">
+      <c r="P16" s="192">
         <v>-9.76</v>
       </c>
-      <c r="Q16" s="185">
+      <c r="Q16" s="194">
         <v>-11.21</v>
       </c>
-      <c r="R16" s="186">
+      <c r="R16" s="195">
         <v>-12.68</v>
       </c>
-      <c r="S16" s="187">
+      <c r="S16" s="184">
         <v>-21.41</v>
       </c>
-      <c r="T16" s="190">
-        <v>-40.63</v>
+      <c r="T16" s="185">
+        <v>-40.99</v>
       </c>
     </row>
     <row r="17">
@@ -5054,38 +5054,38 @@
       <c r="I17" s="197">
         <v>8.25</v>
       </c>
-      <c r="J17" s="206">
+      <c r="J17" s="204">
         <v>0.41</v>
       </c>
-      <c r="K17" s="205">
+      <c r="K17" s="198">
         <v>-3.58</v>
       </c>
-      <c r="L17" s="198">
+      <c r="L17" s="200">
         <v>-3.03</v>
       </c>
-      <c r="M17" s="207">
+      <c r="M17" s="201">
         <v>-0.55</v>
       </c>
       <c r="N17" s="199">
         <v>-1.79</v>
       </c>
-      <c r="O17" s="208">
+      <c r="O17" s="205">
         <v>-0.41</v>
       </c>
-      <c r="P17" s="204">
+      <c r="P17" s="206">
         <v>7.7</v>
       </c>
       <c r="Q17" s="196">
         <v>5.23</v>
       </c>
-      <c r="R17" s="200">
+      <c r="R17" s="202">
         <v>3.03</v>
       </c>
-      <c r="S17" s="201">
+      <c r="S17" s="207">
         <v>0</v>
       </c>
-      <c r="T17" s="202">
-        <v>-5.64</v>
+      <c r="T17" s="208">
+        <v>-3.99</v>
       </c>
     </row>
     <row r="18">
@@ -5147,41 +5147,41 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="215">
+      <c r="I19" s="219">
         <v>43.75</v>
       </c>
-      <c r="J19" s="216">
+      <c r="J19" s="220">
         <v>31.25</v>
       </c>
-      <c r="K19" s="218">
+      <c r="K19" s="209">
         <v>25</v>
       </c>
-      <c r="L19" s="217">
+      <c r="L19" s="216">
         <v>18.75</v>
       </c>
-      <c r="M19" s="212">
+      <c r="M19" s="215">
         <v>31.25</v>
       </c>
-      <c r="N19" s="213">
+      <c r="N19" s="217">
         <v>37.5</v>
       </c>
-      <c r="O19" s="220">
+      <c r="O19" s="218">
         <v>31.25</v>
       </c>
-      <c r="P19" s="209">
+      <c r="P19" s="210">
         <v>37.5</v>
       </c>
-      <c r="Q19" s="210">
+      <c r="Q19" s="212">
         <v>37.5</v>
       </c>
-      <c r="R19" s="219">
+      <c r="R19" s="213">
         <v>37.5</v>
       </c>
-      <c r="S19" s="211">
+      <c r="S19" s="214">
         <v>31.25</v>
       </c>
-      <c r="T19" s="214">
-        <v>37.5</v>
+      <c r="T19" s="211">
+        <v>43.75</v>
       </c>
     </row>
     <row r="20">
@@ -5195,41 +5195,41 @@
       <c r="F20" t="str"/>
       <c r="G20" t="str"/>
       <c r="H20" t="str"/>
-      <c r="I20" s="229">
+      <c r="I20" s="222">
         <v>3.11</v>
       </c>
-      <c r="J20" s="230">
+      <c r="J20" s="228">
         <v>-2.73</v>
       </c>
-      <c r="K20" s="221">
+      <c r="K20" s="223">
         <v>-4.91</v>
       </c>
-      <c r="L20" s="231">
+      <c r="L20" s="229">
         <v>-7.8</v>
       </c>
-      <c r="M20" s="228">
+      <c r="M20" s="226">
         <v>-5.55</v>
       </c>
-      <c r="N20" s="225">
+      <c r="N20" s="231">
         <v>-5.78</v>
       </c>
-      <c r="O20" s="232">
+      <c r="O20" s="224">
         <v>-6.29</v>
       </c>
-      <c r="P20" s="226">
+      <c r="P20" s="227">
         <v>-4.87</v>
       </c>
-      <c r="Q20" s="227">
+      <c r="Q20" s="232">
         <v>-5.25</v>
       </c>
-      <c r="R20" s="222">
+      <c r="R20" s="221">
         <v>-5.94</v>
       </c>
-      <c r="S20" s="223">
+      <c r="S20" s="225">
         <v>-6.59</v>
       </c>
-      <c r="T20" s="224">
-        <v>33.58</v>
+      <c r="T20" s="230">
+        <v>36.41</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/金田路/index.xlsx
+++ b/youzi/金田路/index.xlsx
@@ -45,7 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,43 +57,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,13 +177,751 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15361"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C78A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77882"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBC73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2AA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B461"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,43 +933,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15361"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4DB665"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,19 +993,379 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CC93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,1170 +1377,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77882"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBC73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4DB665"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2AA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA3D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBE2736"/>
         <bgColor/>
       </patternFill>
@@ -1383,24 +1395,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF22913C"/>
         <bgColor/>
       </patternFill>
@@ -1413,7 +1407,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4106,7 +4106,7 @@
       <c r="C2" t="str">
         <v>603124</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="2" t="str">
         <v>净买: 3338.76万</v>
       </c>
       <c r="E2">
@@ -4121,41 +4121,41 @@
       <c r="H2">
         <v>526.19</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="3">
         <v>12.88</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="9">
         <v>-12.55</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="5">
         <v>-22.7</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="6">
         <v>-26.47</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="7">
         <v>-25.17</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="10">
         <v>-30.67</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="11">
         <v>-32.55</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="13">
         <v>-31.88</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="4">
         <v>-29.12</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="1">
         <v>-30.52</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="12">
         <v>-28.5</v>
       </c>
-      <c r="T2" s="3">
-        <v>87.35</v>
+      <c r="T2" s="8">
+        <v>98</v>
       </c>
     </row>
     <row r="3">
@@ -4168,7 +4168,7 @@
       <c r="C3" t="str">
         <v>605298</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="26" t="str">
         <v>净卖: -183.82万</v>
       </c>
       <c r="E3">
@@ -4189,35 +4189,35 @@
       <c r="J3" s="15">
         <v>-1.99</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="17">
         <v>-0.75</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="18">
         <v>3.41</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="24">
         <v>7.06</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="22">
         <v>9.39</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="16">
         <v>5.32</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="25">
         <v>4.24</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="19">
         <v>4.98</v>
       </c>
       <c r="R3" s="20">
         <v>6.56</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="21">
         <v>4.73</v>
       </c>
       <c r="T3" s="23">
-        <v>395.18</v>
+        <v>419.02</v>
       </c>
     </row>
     <row r="4">
@@ -4230,7 +4230,7 @@
       <c r="C4" t="str">
         <v>600418</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="30" t="str">
         <v>净卖: -8419.55万</v>
       </c>
       <c r="E4">
@@ -4245,41 +4245,41 @@
       <c r="H4">
         <v>-0.78</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="37">
         <v>-6.97</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="33">
         <v>-8.32</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="34">
         <v>-7.89</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="38">
         <v>-7.79</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="39">
         <v>1.42</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="27">
         <v>3.29</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="35">
         <v>10.45</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="28">
         <v>15.53</v>
       </c>
-      <c r="Q4" s="37">
+      <c r="Q4" s="31">
         <v>12.95</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="32">
         <v>13.61</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="29">
         <v>11.08</v>
       </c>
-      <c r="T4" s="29">
-        <v>20.26</v>
+      <c r="T4" s="36">
+        <v>17.08</v>
       </c>
     </row>
     <row r="5">
@@ -4292,7 +4292,7 @@
       <c r="C5" t="str">
         <v>002856</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="49" t="str">
         <v>净买: 382.36万</v>
       </c>
       <c r="E5">
@@ -4307,41 +4307,41 @@
       <c r="H5">
         <v>0.25</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="45">
         <v>-10</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="50">
         <v>-0.99</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="42">
         <v>-1.82</v>
       </c>
       <c r="L5" s="43">
         <v>-10.66</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="44">
         <v>-12.81</v>
       </c>
-      <c r="N5" s="50">
+      <c r="N5" s="47">
         <v>-10.33</v>
       </c>
       <c r="O5" s="51">
         <v>-9.92</v>
       </c>
-      <c r="P5" s="52">
+      <c r="P5" s="48">
         <v>-11.24</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="52">
         <v>-10.25</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="40">
         <v>-11.07</v>
       </c>
       <c r="S5" s="46">
         <v>-12.73</v>
       </c>
-      <c r="T5" s="40">
-        <v>3.72</v>
+      <c r="T5" s="41">
+        <v>3.14</v>
       </c>
     </row>
     <row r="6">
@@ -4354,7 +4354,7 @@
       <c r="C6" t="str">
         <v>001331</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="63" t="str">
         <v>净买: 966.34万</v>
       </c>
       <c r="E6">
@@ -4369,41 +4369,41 @@
       <c r="H6">
         <v>10.01</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="64">
         <v>0</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="55">
         <v>-9.55</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="57">
         <v>-18.58</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="61">
         <v>-22.16</v>
       </c>
-      <c r="M6" s="57">
+      <c r="M6" s="58">
         <v>-22.81</v>
       </c>
-      <c r="N6" s="65">
+      <c r="N6" s="59">
         <v>-22.42</v>
       </c>
-      <c r="O6" s="63">
+      <c r="O6" s="65">
         <v>-22.29</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="53">
         <v>-22.03</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="62">
         <v>-18.52</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="54">
         <v>-16.83</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="60">
         <v>-16.76</v>
       </c>
-      <c r="T6" s="60">
-        <v>231.51</v>
+      <c r="T6" s="56">
+        <v>221.83</v>
       </c>
     </row>
     <row r="7">
@@ -4416,7 +4416,7 @@
       <c r="C7" t="str">
         <v>605169</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="74" t="str">
         <v>净卖: -1118.05万</v>
       </c>
       <c r="E7">
@@ -4431,41 +4431,41 @@
       <c r="H7">
         <v>-4.72</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="68">
         <v>15.46</v>
       </c>
-      <c r="J7" s="78">
+      <c r="J7" s="69">
         <v>12.98</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="75">
         <v>2.95</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="76">
         <v>-4.72</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="77">
         <v>-3.13</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="70">
         <v>-5.78</v>
       </c>
-      <c r="O7" s="73">
+      <c r="O7" s="78">
         <v>-5.01</v>
       </c>
-      <c r="P7" s="74">
+      <c r="P7" s="66">
         <v>-6.43</v>
       </c>
-      <c r="Q7" s="75">
+      <c r="Q7" s="67">
         <v>-10.5</v>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="71">
         <v>-9.79</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="72">
         <v>-11.15</v>
       </c>
-      <c r="T7" s="70">
-        <v>-25.66</v>
+      <c r="T7" s="73">
+        <v>-25.55</v>
       </c>
     </row>
     <row r="8">
@@ -4478,7 +4478,7 @@
       <c r="C8" t="str">
         <v>836699</v>
       </c>
-      <c r="D8" s="87" t="str">
+      <c r="D8" s="86" t="str">
         <v>净卖: -801.39万</v>
       </c>
       <c r="E8">
@@ -4493,40 +4493,40 @@
       <c r="H8">
         <v>1.68</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="80">
         <v>27.86</v>
       </c>
-      <c r="J8" s="90">
+      <c r="J8" s="87">
         <v>25.31</v>
       </c>
-      <c r="K8" s="88">
+      <c r="K8" s="84">
         <v>20.9</v>
       </c>
-      <c r="L8" s="91">
+      <c r="L8" s="88">
         <v>14.59</v>
       </c>
-      <c r="M8" s="79">
+      <c r="M8" s="85">
         <v>31.58</v>
       </c>
-      <c r="N8" s="89">
+      <c r="N8" s="82">
         <v>29.44</v>
       </c>
-      <c r="O8" s="81">
+      <c r="O8" s="89">
         <v>22.64</v>
       </c>
-      <c r="P8" s="82">
+      <c r="P8" s="90">
         <v>24.9</v>
       </c>
-      <c r="Q8" s="85">
+      <c r="Q8" s="83">
         <v>20.99</v>
       </c>
-      <c r="R8" s="86">
+      <c r="R8" s="91">
         <v>18.14</v>
       </c>
-      <c r="S8" s="80">
+      <c r="S8" s="79">
         <v>36.74</v>
       </c>
-      <c r="T8" s="83">
+      <c r="T8" s="81">
         <v>30.08</v>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       <c r="C9" t="str">
         <v>301632</v>
       </c>
-      <c r="D9" s="94" t="str">
+      <c r="D9" s="93" t="str">
         <v>净买: 2340.61万</v>
       </c>
       <c r="E9">
@@ -4555,41 +4555,41 @@
       <c r="H9">
         <v>2.77</v>
       </c>
-      <c r="I9" s="95">
+      <c r="I9" s="94">
         <v>-13.93</v>
       </c>
-      <c r="J9" s="100">
+      <c r="J9" s="103">
         <v>-17.96</v>
       </c>
-      <c r="K9" s="103">
+      <c r="K9" s="104">
         <v>-18.95</v>
       </c>
-      <c r="L9" s="96">
+      <c r="L9" s="99">
         <v>-17</v>
       </c>
-      <c r="M9" s="97">
+      <c r="M9" s="100">
         <v>-21.23</v>
       </c>
-      <c r="N9" s="101">
+      <c r="N9" s="95">
         <v>-26.34</v>
       </c>
-      <c r="O9" s="102">
+      <c r="O9" s="96">
         <v>-26.39</v>
       </c>
-      <c r="P9" s="104">
+      <c r="P9" s="97">
         <v>-25.82</v>
       </c>
-      <c r="Q9" s="98">
+      <c r="Q9" s="101">
         <v>-28.19</v>
       </c>
-      <c r="R9" s="99">
+      <c r="R9" s="102">
         <v>-30.97</v>
       </c>
       <c r="S9" s="92">
         <v>-30.82</v>
       </c>
-      <c r="T9" s="93">
-        <v>-53.43</v>
+      <c r="T9" s="98">
+        <v>-54.29</v>
       </c>
     </row>
     <row r="10">
@@ -4617,41 +4617,41 @@
       <c r="H10">
         <v>2.78</v>
       </c>
-      <c r="I10" s="106">
+      <c r="I10" s="115">
         <v>16.75</v>
       </c>
-      <c r="J10" s="117">
+      <c r="J10" s="110">
         <v>1.59</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="116">
         <v>0.16</v>
       </c>
-      <c r="L10" s="111">
+      <c r="L10" s="114">
         <v>-2.23</v>
       </c>
-      <c r="M10" s="107">
+      <c r="M10" s="106">
         <v>5.35</v>
       </c>
-      <c r="N10" s="112">
+      <c r="N10" s="111">
         <v>8.32</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="107">
         <v>9.38</v>
       </c>
-      <c r="P10" s="109">
+      <c r="P10" s="108">
         <v>10.44</v>
       </c>
-      <c r="Q10" s="115">
+      <c r="Q10" s="112">
         <v>8.64</v>
       </c>
       <c r="R10" s="113">
         <v>4.13</v>
       </c>
-      <c r="S10" s="114">
+      <c r="S10" s="117">
         <v>3.34</v>
       </c>
-      <c r="T10" s="116">
-        <v>7.31</v>
+      <c r="T10" s="109">
+        <v>3.07</v>
       </c>
     </row>
     <row r="11">
@@ -4664,7 +4664,7 @@
       <c r="C11" t="str">
         <v>000069</v>
       </c>
-      <c r="D11" s="130" t="str">
+      <c r="D11" s="125" t="str">
         <v>净买: 3152.70万</v>
       </c>
       <c r="E11">
@@ -4679,41 +4679,41 @@
       <c r="H11">
         <v>1.88</v>
       </c>
-      <c r="I11" s="124">
+      <c r="I11" s="126">
         <v>8.12</v>
       </c>
-      <c r="J11" s="121">
+      <c r="J11" s="129">
         <v>3.69</v>
       </c>
-      <c r="K11" s="125">
+      <c r="K11" s="120">
         <v>4.06</v>
       </c>
-      <c r="L11" s="126">
+      <c r="L11" s="121">
         <v>2.95</v>
       </c>
-      <c r="M11" s="118">
+      <c r="M11" s="130">
         <v>4.8</v>
       </c>
-      <c r="N11" s="122">
+      <c r="N11" s="127">
         <v>0.37</v>
       </c>
-      <c r="O11" s="127">
+      <c r="O11" s="118">
         <v>-2.95</v>
       </c>
-      <c r="P11" s="123">
+      <c r="P11" s="119">
         <v>0</v>
       </c>
-      <c r="Q11" s="128">
+      <c r="Q11" s="124">
         <v>-1.11</v>
       </c>
-      <c r="R11" s="129">
+      <c r="R11" s="122">
         <v>-1.85</v>
       </c>
-      <c r="S11" s="119">
+      <c r="S11" s="128">
         <v>0</v>
       </c>
-      <c r="T11" s="120">
-        <v>-18.82</v>
+      <c r="T11" s="123">
+        <v>-20.3</v>
       </c>
     </row>
     <row r="12">
@@ -4726,7 +4726,7 @@
       <c r="C12" t="str">
         <v>002242</v>
       </c>
-      <c r="D12" s="134" t="str">
+      <c r="D12" s="133" t="str">
         <v>净卖: -1077.90万</v>
       </c>
       <c r="E12">
@@ -4741,19 +4741,19 @@
       <c r="H12">
         <v>10.04</v>
       </c>
-      <c r="I12" s="140">
+      <c r="I12" s="141">
         <v>0</v>
       </c>
-      <c r="J12" s="141">
+      <c r="J12" s="142">
         <v>-4.93</v>
       </c>
-      <c r="K12" s="139">
+      <c r="K12" s="134">
         <v>-3.04</v>
       </c>
       <c r="L12" s="135">
         <v>-11.42</v>
       </c>
-      <c r="M12" s="142">
+      <c r="M12" s="143">
         <v>-11.83</v>
       </c>
       <c r="N12" s="136">
@@ -4765,17 +4765,17 @@
       <c r="P12" s="137">
         <v>-14.71</v>
       </c>
-      <c r="Q12" s="143">
+      <c r="Q12" s="138">
         <v>-15.37</v>
       </c>
-      <c r="R12" s="132">
+      <c r="R12" s="139">
         <v>-14.13</v>
       </c>
-      <c r="S12" s="138">
+      <c r="S12" s="132">
         <v>-14.13</v>
       </c>
-      <c r="T12" s="133">
-        <v>-12.16</v>
+      <c r="T12" s="140">
+        <v>-6.57</v>
       </c>
     </row>
     <row r="13">
@@ -4788,7 +4788,7 @@
       <c r="C13" t="str">
         <v>603877</v>
       </c>
-      <c r="D13" s="152" t="str">
+      <c r="D13" s="151" t="str">
         <v>净卖: -596.03万</v>
       </c>
       <c r="E13">
@@ -4803,22 +4803,22 @@
       <c r="H13">
         <v>3.85</v>
       </c>
-      <c r="I13" s="147">
+      <c r="I13" s="145">
         <v>5.94</v>
       </c>
-      <c r="J13" s="148">
+      <c r="J13" s="152">
         <v>0</v>
       </c>
-      <c r="K13" s="153">
+      <c r="K13" s="149">
         <v>-6.18</v>
       </c>
-      <c r="L13" s="151">
+      <c r="L13" s="153">
         <v>-4.29</v>
       </c>
-      <c r="M13" s="154">
+      <c r="M13" s="146">
         <v>-4.94</v>
       </c>
-      <c r="N13" s="155">
+      <c r="N13" s="147">
         <v>-5</v>
       </c>
       <c r="O13" s="156">
@@ -4827,17 +4827,17 @@
       <c r="P13" s="144">
         <v>-3.76</v>
       </c>
-      <c r="Q13" s="145">
+      <c r="Q13" s="154">
         <v>-4.12</v>
       </c>
-      <c r="R13" s="149">
+      <c r="R13" s="148">
         <v>-4.24</v>
       </c>
-      <c r="S13" s="146">
+      <c r="S13" s="155">
         <v>-5.88</v>
       </c>
       <c r="T13" s="150">
-        <v>-11.24</v>
+        <v>-15.71</v>
       </c>
     </row>
     <row r="14">
@@ -4865,41 +4865,41 @@
       <c r="H14">
         <v>-6.54</v>
       </c>
-      <c r="I14" s="160">
+      <c r="I14" s="161">
         <v>-3.72</v>
       </c>
-      <c r="J14" s="161">
+      <c r="J14" s="169">
         <v>-9.38</v>
       </c>
-      <c r="K14" s="168">
+      <c r="K14" s="164">
         <v>-2.23</v>
       </c>
-      <c r="L14" s="169">
+      <c r="L14" s="165">
         <v>-4.26</v>
       </c>
-      <c r="M14" s="159">
+      <c r="M14" s="166">
         <v>-0.51</v>
       </c>
-      <c r="N14" s="157">
+      <c r="N14" s="167">
         <v>9.31</v>
       </c>
-      <c r="O14" s="163">
+      <c r="O14" s="162">
         <v>5.63</v>
       </c>
-      <c r="P14" s="164">
+      <c r="P14" s="157">
         <v>5.63</v>
       </c>
-      <c r="Q14" s="165">
+      <c r="Q14" s="159">
         <v>11.51</v>
       </c>
-      <c r="R14" s="166">
+      <c r="R14" s="163">
         <v>11.89</v>
       </c>
-      <c r="S14" s="167">
+      <c r="S14" s="168">
         <v>2.92</v>
       </c>
-      <c r="T14" s="162">
-        <v>-2.13</v>
+      <c r="T14" s="160">
+        <v>-6.48</v>
       </c>
     </row>
     <row r="15">
@@ -4912,7 +4912,7 @@
       <c r="C15" t="str">
         <v>002589</v>
       </c>
-      <c r="D15" s="180" t="str">
+      <c r="D15" s="175" t="str">
         <v>净买: 1428.73万</v>
       </c>
       <c r="E15">
@@ -4927,25 +4927,25 @@
       <c r="H15">
         <v>-5.54</v>
       </c>
-      <c r="I15" s="174">
+      <c r="I15" s="181">
         <v>-4.74</v>
       </c>
-      <c r="J15" s="171">
+      <c r="J15" s="176">
         <v>-11.96</v>
       </c>
-      <c r="K15" s="175">
+      <c r="K15" s="171">
         <v>-19.86</v>
       </c>
-      <c r="L15" s="178">
+      <c r="L15" s="177">
         <v>-20.77</v>
       </c>
-      <c r="M15" s="181">
+      <c r="M15" s="178">
         <v>-18.96</v>
       </c>
-      <c r="N15" s="176">
+      <c r="N15" s="172">
         <v>-23.25</v>
       </c>
-      <c r="O15" s="172">
+      <c r="O15" s="173">
         <v>-23.7</v>
       </c>
       <c r="P15" s="179">
@@ -4957,11 +4957,11 @@
       <c r="R15" s="170">
         <v>-20.32</v>
       </c>
-      <c r="S15" s="173">
+      <c r="S15" s="180">
         <v>-22.8</v>
       </c>
-      <c r="T15" s="177">
-        <v>-24.38</v>
+      <c r="T15" s="174">
+        <v>-27.31</v>
       </c>
     </row>
     <row r="16">
@@ -4974,7 +4974,7 @@
       <c r="C16" t="str">
         <v>605255</v>
       </c>
-      <c r="D16" s="183" t="str">
+      <c r="D16" s="193" t="str">
         <v>净卖: -745.64万</v>
       </c>
       <c r="E16">
@@ -4989,13 +4989,13 @@
       <c r="H16">
         <v>-10</v>
       </c>
-      <c r="I16" s="186">
+      <c r="I16" s="194">
         <v>0</v>
       </c>
-      <c r="J16" s="187">
+      <c r="J16" s="186">
         <v>-10</v>
       </c>
-      <c r="K16" s="193">
+      <c r="K16" s="188">
         <v>-1</v>
       </c>
       <c r="L16" s="189">
@@ -5004,26 +5004,26 @@
       <c r="M16" s="190">
         <v>-17.03</v>
       </c>
-      <c r="N16" s="191">
+      <c r="N16" s="184">
         <v>-11.34</v>
       </c>
-      <c r="O16" s="188">
+      <c r="O16" s="195">
         <v>-8.27</v>
       </c>
-      <c r="P16" s="192">
+      <c r="P16" s="191">
         <v>-9.76</v>
       </c>
-      <c r="Q16" s="194">
+      <c r="Q16" s="192">
         <v>-11.21</v>
       </c>
-      <c r="R16" s="195">
+      <c r="R16" s="183">
         <v>-12.68</v>
       </c>
-      <c r="S16" s="184">
+      <c r="S16" s="187">
         <v>-21.41</v>
       </c>
       <c r="T16" s="185">
-        <v>-40.99</v>
+        <v>-45.57</v>
       </c>
     </row>
     <row r="17">
@@ -5036,7 +5036,7 @@
       <c r="C17" t="str">
         <v>601139</v>
       </c>
-      <c r="D17" s="203" t="str">
+      <c r="D17" s="199" t="str">
         <v>净卖: -3779.77万</v>
       </c>
       <c r="E17">
@@ -5054,38 +5054,38 @@
       <c r="I17" s="197">
         <v>8.25</v>
       </c>
-      <c r="J17" s="204">
+      <c r="J17" s="206">
         <v>0.41</v>
       </c>
-      <c r="K17" s="198">
+      <c r="K17" s="204">
         <v>-3.58</v>
       </c>
       <c r="L17" s="200">
         <v>-3.03</v>
       </c>
-      <c r="M17" s="201">
+      <c r="M17" s="207">
         <v>-0.55</v>
       </c>
-      <c r="N17" s="199">
+      <c r="N17" s="201">
         <v>-1.79</v>
       </c>
       <c r="O17" s="205">
         <v>-0.41</v>
       </c>
-      <c r="P17" s="206">
+      <c r="P17" s="198">
         <v>7.7</v>
       </c>
-      <c r="Q17" s="196">
+      <c r="Q17" s="208">
         <v>5.23</v>
       </c>
       <c r="R17" s="202">
         <v>3.03</v>
       </c>
-      <c r="S17" s="207">
+      <c r="S17" s="203">
         <v>0</v>
       </c>
-      <c r="T17" s="208">
-        <v>-3.99</v>
+      <c r="T17" s="196">
+        <v>-2.89</v>
       </c>
     </row>
     <row r="18">
@@ -5147,40 +5147,40 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="219">
+      <c r="I19" s="212">
         <v>43.75</v>
       </c>
-      <c r="J19" s="220">
+      <c r="J19" s="218">
         <v>31.25</v>
       </c>
-      <c r="K19" s="209">
+      <c r="K19" s="219">
         <v>25</v>
       </c>
-      <c r="L19" s="216">
+      <c r="L19" s="213">
         <v>18.75</v>
       </c>
-      <c r="M19" s="215">
+      <c r="M19" s="220">
         <v>31.25</v>
       </c>
-      <c r="N19" s="217">
+      <c r="N19" s="209">
         <v>37.5</v>
       </c>
-      <c r="O19" s="218">
+      <c r="O19" s="214">
         <v>31.25</v>
       </c>
-      <c r="P19" s="210">
+      <c r="P19" s="215">
         <v>37.5</v>
       </c>
-      <c r="Q19" s="212">
+      <c r="Q19" s="210">
         <v>37.5</v>
       </c>
-      <c r="R19" s="213">
+      <c r="R19" s="216">
         <v>37.5</v>
       </c>
-      <c r="S19" s="214">
+      <c r="S19" s="211">
         <v>31.25</v>
       </c>
-      <c r="T19" s="211">
+      <c r="T19" s="217">
         <v>43.75</v>
       </c>
     </row>
@@ -5195,41 +5195,41 @@
       <c r="F20" t="str"/>
       <c r="G20" t="str"/>
       <c r="H20" t="str"/>
-      <c r="I20" s="222">
+      <c r="I20" s="224">
         <v>3.11</v>
       </c>
-      <c r="J20" s="228">
+      <c r="J20" s="227">
         <v>-2.73</v>
       </c>
-      <c r="K20" s="223">
+      <c r="K20" s="231">
         <v>-4.91</v>
       </c>
-      <c r="L20" s="229">
+      <c r="L20" s="232">
         <v>-7.8</v>
       </c>
-      <c r="M20" s="226">
+      <c r="M20" s="228">
         <v>-5.55</v>
       </c>
-      <c r="N20" s="231">
+      <c r="N20" s="225">
         <v>-5.78</v>
       </c>
-      <c r="O20" s="224">
+      <c r="O20" s="229">
         <v>-6.29</v>
       </c>
-      <c r="P20" s="227">
+      <c r="P20" s="221">
         <v>-4.87</v>
       </c>
-      <c r="Q20" s="232">
+      <c r="Q20" s="230">
         <v>-5.25</v>
       </c>
-      <c r="R20" s="221">
+      <c r="R20" s="226">
         <v>-5.94</v>
       </c>
-      <c r="S20" s="225">
+      <c r="S20" s="222">
         <v>-6.59</v>
       </c>
-      <c r="T20" s="230">
-        <v>36.41</v>
+      <c r="T20" s="223">
+        <v>36.72</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/金田路/index.xlsx
+++ b/youzi/金田路/index.xlsx
@@ -45,37 +45,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15361"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,25 +219,673 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C78A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77882"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,25 +903,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBC73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4DB665"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2AA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,19 +993,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,13 +1023,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15361"/>
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF36AC51"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,1219 +1167,247 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE77A84"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77882"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBC73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2AA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4DB665"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CC93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4106,7 +4106,7 @@
       <c r="C2" t="str">
         <v>603124</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="12" t="str">
         <v>净买: 3338.76万</v>
       </c>
       <c r="E2">
@@ -4121,41 +4121,41 @@
       <c r="H2">
         <v>526.19</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="7">
         <v>12.88</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="3">
         <v>-12.55</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="13">
         <v>-22.7</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="8">
         <v>-26.47</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="10">
         <v>-25.17</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="4">
         <v>-30.67</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="1">
         <v>-32.55</v>
       </c>
-      <c r="P2" s="13">
+      <c r="P2" s="5">
         <v>-31.88</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="11">
         <v>-29.12</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="2">
         <v>-30.52</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="9">
         <v>-28.5</v>
       </c>
-      <c r="T2" s="8">
-        <v>98</v>
+      <c r="T2" s="6">
+        <v>100.8</v>
       </c>
     </row>
     <row r="3">
@@ -4168,7 +4168,7 @@
       <c r="C3" t="str">
         <v>605298</v>
       </c>
-      <c r="D3" s="26" t="str">
+      <c r="D3" s="18" t="str">
         <v>净卖: -183.82万</v>
       </c>
       <c r="E3">
@@ -4183,41 +4183,41 @@
       <c r="H3">
         <v>-4.14</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="19">
         <v>-6.15</v>
       </c>
       <c r="J3" s="15">
         <v>-1.99</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="20">
         <v>-0.75</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="26">
         <v>3.41</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="16">
         <v>7.06</v>
       </c>
-      <c r="N3" s="22">
+      <c r="N3" s="17">
         <v>9.39</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="21">
         <v>5.32</v>
       </c>
-      <c r="P3" s="25">
+      <c r="P3" s="22">
         <v>4.24</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="24">
         <v>4.98</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="14">
         <v>6.56</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="25">
         <v>4.73</v>
       </c>
       <c r="T3" s="23">
-        <v>419.02</v>
+        <v>425.5</v>
       </c>
     </row>
     <row r="4">
@@ -4230,7 +4230,7 @@
       <c r="C4" t="str">
         <v>600418</v>
       </c>
-      <c r="D4" s="30" t="str">
+      <c r="D4" s="27" t="str">
         <v>净卖: -8419.55万</v>
       </c>
       <c r="E4">
@@ -4245,41 +4245,41 @@
       <c r="H4">
         <v>-0.78</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="28">
         <v>-6.97</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="34">
         <v>-8.32</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="35">
         <v>-7.89</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="31">
         <v>-7.79</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="29">
         <v>1.42</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="39">
         <v>3.29</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="36">
         <v>10.45</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="37">
         <v>15.53</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="30">
         <v>12.95</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="38">
         <v>13.61</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="32">
         <v>11.08</v>
       </c>
-      <c r="T4" s="36">
-        <v>17.08</v>
+      <c r="T4" s="33">
+        <v>28.79</v>
       </c>
     </row>
     <row r="5">
@@ -4292,7 +4292,7 @@
       <c r="C5" t="str">
         <v>002856</v>
       </c>
-      <c r="D5" s="49" t="str">
+      <c r="D5" s="48" t="str">
         <v>净买: 382.36万</v>
       </c>
       <c r="E5">
@@ -4307,41 +4307,41 @@
       <c r="H5">
         <v>0.25</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="49">
         <v>-10</v>
       </c>
       <c r="J5" s="50">
         <v>-0.99</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="52">
         <v>-1.82</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="40">
         <v>-10.66</v>
       </c>
       <c r="M5" s="44">
         <v>-12.81</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="45">
         <v>-10.33</v>
       </c>
-      <c r="O5" s="51">
+      <c r="O5" s="41">
         <v>-9.92</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="42">
         <v>-11.24</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="46">
         <v>-10.25</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="51">
         <v>-11.07</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="47">
         <v>-12.73</v>
       </c>
-      <c r="T5" s="41">
-        <v>3.14</v>
+      <c r="T5" s="43">
+        <v>8.43</v>
       </c>
     </row>
     <row r="6">
@@ -4369,41 +4369,41 @@
       <c r="H6">
         <v>10.01</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="55">
         <v>0</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="64">
         <v>-9.55</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="56">
         <v>-18.58</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="58">
         <v>-22.16</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="65">
         <v>-22.81</v>
       </c>
       <c r="N6" s="59">
         <v>-22.42</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="53">
         <v>-22.29</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="60">
         <v>-22.03</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="61">
         <v>-18.52</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="57">
         <v>-16.83</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="54">
         <v>-16.76</v>
       </c>
-      <c r="T6" s="56">
-        <v>221.83</v>
+      <c r="T6" s="62">
+        <v>189.67</v>
       </c>
     </row>
     <row r="7">
@@ -4416,7 +4416,7 @@
       <c r="C7" t="str">
         <v>605169</v>
       </c>
-      <c r="D7" s="74" t="str">
+      <c r="D7" s="75" t="str">
         <v>净卖: -1118.05万</v>
       </c>
       <c r="E7">
@@ -4431,41 +4431,41 @@
       <c r="H7">
         <v>-4.72</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="71">
         <v>15.46</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="72">
         <v>12.98</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="78">
         <v>2.95</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="66">
         <v>-4.72</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="67">
         <v>-3.13</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="68">
         <v>-5.78</v>
       </c>
-      <c r="O7" s="78">
+      <c r="O7" s="73">
         <v>-5.01</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="77">
         <v>-6.43</v>
       </c>
-      <c r="Q7" s="67">
+      <c r="Q7" s="74">
         <v>-10.5</v>
       </c>
-      <c r="R7" s="71">
+      <c r="R7" s="69">
         <v>-9.79</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="76">
         <v>-11.15</v>
       </c>
-      <c r="T7" s="73">
-        <v>-25.55</v>
+      <c r="T7" s="70">
+        <v>-24.01</v>
       </c>
     </row>
     <row r="8">
@@ -4478,7 +4478,7 @@
       <c r="C8" t="str">
         <v>836699</v>
       </c>
-      <c r="D8" s="86" t="str">
+      <c r="D8" s="91" t="str">
         <v>净卖: -801.39万</v>
       </c>
       <c r="E8">
@@ -4493,40 +4493,40 @@
       <c r="H8">
         <v>1.68</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="88">
         <v>27.86</v>
       </c>
-      <c r="J8" s="87">
+      <c r="J8" s="89">
         <v>25.31</v>
       </c>
       <c r="K8" s="84">
         <v>20.9</v>
       </c>
-      <c r="L8" s="88">
+      <c r="L8" s="79">
         <v>14.59</v>
       </c>
       <c r="M8" s="85">
         <v>31.58</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="80">
         <v>29.44</v>
       </c>
-      <c r="O8" s="89">
+      <c r="O8" s="90">
         <v>22.64</v>
       </c>
-      <c r="P8" s="90">
+      <c r="P8" s="86">
         <v>24.9</v>
       </c>
-      <c r="Q8" s="83">
+      <c r="Q8" s="81">
         <v>20.99</v>
       </c>
-      <c r="R8" s="91">
+      <c r="R8" s="87">
         <v>18.14</v>
       </c>
-      <c r="S8" s="79">
+      <c r="S8" s="82">
         <v>36.74</v>
       </c>
-      <c r="T8" s="81">
+      <c r="T8" s="83">
         <v>30.08</v>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       <c r="C9" t="str">
         <v>301632</v>
       </c>
-      <c r="D9" s="93" t="str">
+      <c r="D9" s="102" t="str">
         <v>净买: 2340.61万</v>
       </c>
       <c r="E9">
@@ -4555,41 +4555,41 @@
       <c r="H9">
         <v>2.77</v>
       </c>
-      <c r="I9" s="94">
+      <c r="I9" s="103">
         <v>-13.93</v>
       </c>
-      <c r="J9" s="103">
+      <c r="J9" s="94">
         <v>-17.96</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="97">
         <v>-18.95</v>
       </c>
-      <c r="L9" s="99">
+      <c r="L9" s="104">
         <v>-17</v>
       </c>
-      <c r="M9" s="100">
+      <c r="M9" s="95">
         <v>-21.23</v>
       </c>
-      <c r="N9" s="95">
+      <c r="N9" s="98">
         <v>-26.34</v>
       </c>
-      <c r="O9" s="96">
+      <c r="O9" s="92">
         <v>-26.39</v>
       </c>
-      <c r="P9" s="97">
+      <c r="P9" s="99">
         <v>-25.82</v>
       </c>
-      <c r="Q9" s="101">
+      <c r="Q9" s="100">
         <v>-28.19</v>
       </c>
-      <c r="R9" s="102">
+      <c r="R9" s="96">
         <v>-30.97</v>
       </c>
-      <c r="S9" s="92">
+      <c r="S9" s="101">
         <v>-30.82</v>
       </c>
-      <c r="T9" s="98">
-        <v>-54.29</v>
+      <c r="T9" s="93">
+        <v>-54.75</v>
       </c>
     </row>
     <row r="10">
@@ -4602,7 +4602,7 @@
       <c r="C10" t="str">
         <v>300948</v>
       </c>
-      <c r="D10" s="105" t="str">
+      <c r="D10" s="115" t="str">
         <v>净卖: -709.60万</v>
       </c>
       <c r="E10">
@@ -4617,41 +4617,41 @@
       <c r="H10">
         <v>2.78</v>
       </c>
-      <c r="I10" s="115">
+      <c r="I10" s="116">
         <v>16.75</v>
       </c>
       <c r="J10" s="110">
         <v>1.59</v>
       </c>
-      <c r="K10" s="116">
+      <c r="K10" s="107">
         <v>0.16</v>
       </c>
-      <c r="L10" s="114">
+      <c r="L10" s="117">
         <v>-2.23</v>
       </c>
-      <c r="M10" s="106">
+      <c r="M10" s="111">
         <v>5.35</v>
       </c>
-      <c r="N10" s="111">
+      <c r="N10" s="108">
         <v>8.32</v>
       </c>
-      <c r="O10" s="107">
+      <c r="O10" s="112">
         <v>9.38</v>
       </c>
-      <c r="P10" s="108">
+      <c r="P10" s="113">
         <v>10.44</v>
       </c>
-      <c r="Q10" s="112">
+      <c r="Q10" s="105">
         <v>8.64</v>
       </c>
-      <c r="R10" s="113">
+      <c r="R10" s="114">
         <v>4.13</v>
       </c>
-      <c r="S10" s="117">
+      <c r="S10" s="109">
         <v>3.34</v>
       </c>
-      <c r="T10" s="109">
-        <v>3.07</v>
+      <c r="T10" s="106">
+        <v>6.36</v>
       </c>
     </row>
     <row r="11">
@@ -4664,7 +4664,7 @@
       <c r="C11" t="str">
         <v>000069</v>
       </c>
-      <c r="D11" s="125" t="str">
+      <c r="D11" s="118" t="str">
         <v>净买: 3152.70万</v>
       </c>
       <c r="E11">
@@ -4679,10 +4679,10 @@
       <c r="H11">
         <v>1.88</v>
       </c>
-      <c r="I11" s="126">
+      <c r="I11" s="128">
         <v>8.12</v>
       </c>
-      <c r="J11" s="129">
+      <c r="J11" s="119">
         <v>3.69</v>
       </c>
       <c r="K11" s="120">
@@ -4691,29 +4691,29 @@
       <c r="L11" s="121">
         <v>2.95</v>
       </c>
-      <c r="M11" s="130">
+      <c r="M11" s="124">
         <v>4.8</v>
       </c>
-      <c r="N11" s="127">
+      <c r="N11" s="129">
         <v>0.37</v>
       </c>
-      <c r="O11" s="118">
+      <c r="O11" s="125">
         <v>-2.95</v>
       </c>
-      <c r="P11" s="119">
+      <c r="P11" s="126">
         <v>0</v>
       </c>
-      <c r="Q11" s="124">
+      <c r="Q11" s="122">
         <v>-1.11</v>
       </c>
-      <c r="R11" s="122">
+      <c r="R11" s="130">
         <v>-1.85</v>
       </c>
-      <c r="S11" s="128">
+      <c r="S11" s="123">
         <v>0</v>
       </c>
-      <c r="T11" s="123">
-        <v>-20.3</v>
+      <c r="T11" s="127">
+        <v>-19.56</v>
       </c>
     </row>
     <row r="12">
@@ -4726,7 +4726,7 @@
       <c r="C12" t="str">
         <v>002242</v>
       </c>
-      <c r="D12" s="133" t="str">
+      <c r="D12" s="135" t="str">
         <v>净卖: -1077.90万</v>
       </c>
       <c r="E12">
@@ -4741,41 +4741,41 @@
       <c r="H12">
         <v>10.04</v>
       </c>
-      <c r="I12" s="141">
+      <c r="I12" s="139">
         <v>0</v>
       </c>
       <c r="J12" s="142">
         <v>-4.93</v>
       </c>
-      <c r="K12" s="134">
+      <c r="K12" s="136">
         <v>-3.04</v>
       </c>
-      <c r="L12" s="135">
+      <c r="L12" s="143">
         <v>-11.42</v>
       </c>
-      <c r="M12" s="143">
+      <c r="M12" s="132">
         <v>-11.83</v>
       </c>
-      <c r="N12" s="136">
+      <c r="N12" s="140">
         <v>-15.61</v>
       </c>
-      <c r="O12" s="131">
+      <c r="O12" s="137">
         <v>-15.12</v>
       </c>
-      <c r="P12" s="137">
+      <c r="P12" s="138">
         <v>-14.71</v>
       </c>
-      <c r="Q12" s="138">
+      <c r="Q12" s="133">
         <v>-15.37</v>
       </c>
-      <c r="R12" s="139">
+      <c r="R12" s="141">
         <v>-14.13</v>
       </c>
-      <c r="S12" s="132">
+      <c r="S12" s="131">
         <v>-14.13</v>
       </c>
-      <c r="T12" s="140">
-        <v>-6.57</v>
+      <c r="T12" s="134">
+        <v>-8.38</v>
       </c>
     </row>
     <row r="13">
@@ -4788,7 +4788,7 @@
       <c r="C13" t="str">
         <v>603877</v>
       </c>
-      <c r="D13" s="151" t="str">
+      <c r="D13" s="153" t="str">
         <v>净卖: -596.03万</v>
       </c>
       <c r="E13">
@@ -4803,41 +4803,41 @@
       <c r="H13">
         <v>3.85</v>
       </c>
-      <c r="I13" s="145">
+      <c r="I13" s="147">
         <v>5.94</v>
       </c>
-      <c r="J13" s="152">
+      <c r="J13" s="154">
         <v>0</v>
       </c>
-      <c r="K13" s="149">
+      <c r="K13" s="144">
         <v>-6.18</v>
       </c>
-      <c r="L13" s="153">
+      <c r="L13" s="155">
         <v>-4.29</v>
       </c>
-      <c r="M13" s="146">
+      <c r="M13" s="152">
         <v>-4.94</v>
       </c>
-      <c r="N13" s="147">
+      <c r="N13" s="156">
         <v>-5</v>
       </c>
-      <c r="O13" s="156">
+      <c r="O13" s="145">
         <v>-7.41</v>
       </c>
-      <c r="P13" s="144">
+      <c r="P13" s="148">
         <v>-3.76</v>
       </c>
-      <c r="Q13" s="154">
+      <c r="Q13" s="149">
         <v>-4.12</v>
       </c>
-      <c r="R13" s="148">
+      <c r="R13" s="150">
         <v>-4.24</v>
       </c>
-      <c r="S13" s="155">
+      <c r="S13" s="146">
         <v>-5.88</v>
       </c>
-      <c r="T13" s="150">
-        <v>-15.71</v>
+      <c r="T13" s="151">
+        <v>-15.41</v>
       </c>
     </row>
     <row r="14">
@@ -4850,7 +4850,7 @@
       <c r="C14" t="str">
         <v>603216</v>
       </c>
-      <c r="D14" s="158" t="str">
+      <c r="D14" s="159" t="str">
         <v>净买: 462.51万</v>
       </c>
       <c r="E14">
@@ -4865,41 +4865,41 @@
       <c r="H14">
         <v>-6.54</v>
       </c>
-      <c r="I14" s="161">
+      <c r="I14" s="160">
         <v>-3.72</v>
       </c>
-      <c r="J14" s="169">
+      <c r="J14" s="167">
         <v>-9.38</v>
       </c>
-      <c r="K14" s="164">
+      <c r="K14" s="161">
         <v>-2.23</v>
       </c>
-      <c r="L14" s="165">
+      <c r="L14" s="169">
         <v>-4.26</v>
       </c>
-      <c r="M14" s="166">
+      <c r="M14" s="162">
         <v>-0.51</v>
       </c>
-      <c r="N14" s="167">
+      <c r="N14" s="163">
         <v>9.31</v>
       </c>
-      <c r="O14" s="162">
+      <c r="O14" s="157">
         <v>5.63</v>
       </c>
-      <c r="P14" s="157">
+      <c r="P14" s="168">
         <v>5.63</v>
       </c>
-      <c r="Q14" s="159">
+      <c r="Q14" s="158">
         <v>11.51</v>
       </c>
-      <c r="R14" s="163">
+      <c r="R14" s="164">
         <v>11.89</v>
       </c>
-      <c r="S14" s="168">
+      <c r="S14" s="165">
         <v>2.92</v>
       </c>
-      <c r="T14" s="160">
-        <v>-6.48</v>
+      <c r="T14" s="166">
+        <v>-4.67</v>
       </c>
     </row>
     <row r="15">
@@ -4912,7 +4912,7 @@
       <c r="C15" t="str">
         <v>002589</v>
       </c>
-      <c r="D15" s="175" t="str">
+      <c r="D15" s="174" t="str">
         <v>净买: 1428.73万</v>
       </c>
       <c r="E15">
@@ -4927,41 +4927,41 @@
       <c r="H15">
         <v>-5.54</v>
       </c>
-      <c r="I15" s="181">
+      <c r="I15" s="182">
         <v>-4.74</v>
       </c>
-      <c r="J15" s="176">
+      <c r="J15" s="179">
         <v>-11.96</v>
       </c>
-      <c r="K15" s="171">
+      <c r="K15" s="175">
         <v>-19.86</v>
       </c>
-      <c r="L15" s="177">
+      <c r="L15" s="180">
         <v>-20.77</v>
       </c>
-      <c r="M15" s="178">
+      <c r="M15" s="181">
         <v>-18.96</v>
       </c>
-      <c r="N15" s="172">
+      <c r="N15" s="176">
         <v>-23.25</v>
       </c>
-      <c r="O15" s="173">
+      <c r="O15" s="170">
         <v>-23.7</v>
       </c>
-      <c r="P15" s="179">
+      <c r="P15" s="173">
         <v>-20.77</v>
       </c>
-      <c r="Q15" s="182">
+      <c r="Q15" s="171">
         <v>-19.86</v>
       </c>
-      <c r="R15" s="170">
+      <c r="R15" s="172">
         <v>-20.32</v>
       </c>
-      <c r="S15" s="180">
+      <c r="S15" s="177">
         <v>-22.8</v>
       </c>
-      <c r="T15" s="174">
-        <v>-27.31</v>
+      <c r="T15" s="178">
+        <v>-27.54</v>
       </c>
     </row>
     <row r="16">
@@ -4974,7 +4974,7 @@
       <c r="C16" t="str">
         <v>605255</v>
       </c>
-      <c r="D16" s="193" t="str">
+      <c r="D16" s="188" t="str">
         <v>净卖: -745.64万</v>
       </c>
       <c r="E16">
@@ -4989,41 +4989,41 @@
       <c r="H16">
         <v>-10</v>
       </c>
-      <c r="I16" s="194">
+      <c r="I16" s="189">
         <v>0</v>
       </c>
-      <c r="J16" s="186">
+      <c r="J16" s="183">
         <v>-10</v>
       </c>
-      <c r="K16" s="188">
+      <c r="K16" s="191">
         <v>-1</v>
       </c>
-      <c r="L16" s="189">
+      <c r="L16" s="184">
         <v>-10.9</v>
       </c>
       <c r="M16" s="190">
         <v>-17.03</v>
       </c>
-      <c r="N16" s="184">
+      <c r="N16" s="192">
         <v>-11.34</v>
       </c>
-      <c r="O16" s="195">
+      <c r="O16" s="185">
         <v>-8.27</v>
       </c>
-      <c r="P16" s="191">
+      <c r="P16" s="193">
         <v>-9.76</v>
       </c>
-      <c r="Q16" s="192">
+      <c r="Q16" s="194">
         <v>-11.21</v>
       </c>
-      <c r="R16" s="183">
+      <c r="R16" s="186">
         <v>-12.68</v>
       </c>
       <c r="S16" s="187">
         <v>-21.41</v>
       </c>
-      <c r="T16" s="185">
-        <v>-45.57</v>
+      <c r="T16" s="195">
+        <v>-44.69</v>
       </c>
     </row>
     <row r="17">
@@ -5036,7 +5036,7 @@
       <c r="C17" t="str">
         <v>601139</v>
       </c>
-      <c r="D17" s="199" t="str">
+      <c r="D17" s="203" t="str">
         <v>净卖: -3779.77万</v>
       </c>
       <c r="E17">
@@ -5051,41 +5051,41 @@
       <c r="H17">
         <v>1.68</v>
       </c>
-      <c r="I17" s="197">
+      <c r="I17" s="208">
         <v>8.25</v>
       </c>
-      <c r="J17" s="206">
+      <c r="J17" s="204">
         <v>0.41</v>
       </c>
-      <c r="K17" s="204">
+      <c r="K17" s="205">
         <v>-3.58</v>
       </c>
-      <c r="L17" s="200">
+      <c r="L17" s="196">
         <v>-3.03</v>
       </c>
-      <c r="M17" s="207">
+      <c r="M17" s="206">
         <v>-0.55</v>
       </c>
-      <c r="N17" s="201">
+      <c r="N17" s="200">
         <v>-1.79</v>
       </c>
-      <c r="O17" s="205">
+      <c r="O17" s="201">
         <v>-0.41</v>
       </c>
-      <c r="P17" s="198">
+      <c r="P17" s="197">
         <v>7.7</v>
       </c>
-      <c r="Q17" s="208">
+      <c r="Q17" s="198">
         <v>5.23</v>
       </c>
-      <c r="R17" s="202">
+      <c r="R17" s="199">
         <v>3.03</v>
       </c>
-      <c r="S17" s="203">
+      <c r="S17" s="207">
         <v>0</v>
       </c>
-      <c r="T17" s="196">
-        <v>-2.89</v>
+      <c r="T17" s="202">
+        <v>-3.58</v>
       </c>
     </row>
     <row r="18">
@@ -5147,40 +5147,40 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="212">
+      <c r="I19" s="209">
         <v>43.75</v>
       </c>
-      <c r="J19" s="218">
+      <c r="J19" s="214">
         <v>31.25</v>
       </c>
-      <c r="K19" s="219">
+      <c r="K19" s="215">
         <v>25</v>
       </c>
-      <c r="L19" s="213">
+      <c r="L19" s="216">
         <v>18.75</v>
       </c>
-      <c r="M19" s="220">
+      <c r="M19" s="210">
         <v>31.25</v>
       </c>
-      <c r="N19" s="209">
+      <c r="N19" s="217">
         <v>37.5</v>
       </c>
-      <c r="O19" s="214">
+      <c r="O19" s="211">
         <v>31.25</v>
       </c>
-      <c r="P19" s="215">
+      <c r="P19" s="212">
         <v>37.5</v>
       </c>
-      <c r="Q19" s="210">
+      <c r="Q19" s="218">
         <v>37.5</v>
       </c>
-      <c r="R19" s="216">
+      <c r="R19" s="213">
         <v>37.5</v>
       </c>
-      <c r="S19" s="211">
+      <c r="S19" s="219">
         <v>31.25</v>
       </c>
-      <c r="T19" s="217">
+      <c r="T19" s="220">
         <v>43.75</v>
       </c>
     </row>
@@ -5195,41 +5195,41 @@
       <c r="F20" t="str"/>
       <c r="G20" t="str"/>
       <c r="H20" t="str"/>
-      <c r="I20" s="224">
+      <c r="I20" s="222">
         <v>3.11</v>
       </c>
-      <c r="J20" s="227">
+      <c r="J20" s="223">
         <v>-2.73</v>
       </c>
-      <c r="K20" s="231">
+      <c r="K20" s="224">
         <v>-4.91</v>
       </c>
-      <c r="L20" s="232">
+      <c r="L20" s="230">
         <v>-7.8</v>
       </c>
-      <c r="M20" s="228">
+      <c r="M20" s="232">
         <v>-5.55</v>
       </c>
-      <c r="N20" s="225">
+      <c r="N20" s="227">
         <v>-5.78</v>
       </c>
-      <c r="O20" s="229">
+      <c r="O20" s="225">
         <v>-6.29</v>
       </c>
-      <c r="P20" s="221">
+      <c r="P20" s="231">
         <v>-4.87</v>
       </c>
-      <c r="Q20" s="230">
+      <c r="Q20" s="221">
         <v>-5.25</v>
       </c>
-      <c r="R20" s="226">
+      <c r="R20" s="228">
         <v>-5.94</v>
       </c>
-      <c r="S20" s="222">
+      <c r="S20" s="226">
         <v>-6.59</v>
       </c>
-      <c r="T20" s="223">
-        <v>36.72</v>
+      <c r="T20" s="229">
+        <v>36.69</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/金田路/index.xlsx
+++ b/youzi/金田路/index.xlsx
@@ -63,6 +63,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -87,19 +117,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,7 +171,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15361"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,7 +195,529 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C78A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,31 +729,247 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE77882"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF24993F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15361"/>
+        <fgColor rgb="FF2AA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBC73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4DB665"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF48B461"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,19 +981,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B460"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,13 +1143,253 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,1141 +1401,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C78A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77882"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBC73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4DB665"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF48B461"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2AA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF36AC51"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B460"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDD9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1366,66 +1426,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -4106,7 +4106,7 @@
       <c r="C2" t="str">
         <v>603124</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="5" t="str">
         <v>净买: 3338.76万</v>
       </c>
       <c r="E2">
@@ -4121,41 +4121,41 @@
       <c r="H2">
         <v>526.19</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="12">
         <v>12.88</v>
       </c>
       <c r="J2" s="3">
         <v>-12.55</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="6">
         <v>-22.7</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="4">
         <v>-26.47</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="13">
         <v>-25.17</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="7">
         <v>-30.67</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="8">
         <v>-32.55</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="1">
         <v>-31.88</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="9">
         <v>-29.12</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="10">
         <v>-30.52</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="2">
         <v>-28.5</v>
       </c>
-      <c r="T2" s="6">
-        <v>100.8</v>
+      <c r="T2" s="11">
+        <v>106.26</v>
       </c>
     </row>
     <row r="3">
@@ -4183,41 +4183,41 @@
       <c r="H3">
         <v>-4.14</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="23">
         <v>-6.15</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="26">
         <v>-1.99</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="19">
         <v>-0.75</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="20">
         <v>3.41</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="21">
         <v>7.06</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="14">
         <v>9.39</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="15">
         <v>5.32</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="24">
         <v>4.24</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="22">
         <v>4.98</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="25">
         <v>6.56</v>
       </c>
-      <c r="S3" s="25">
+      <c r="S3" s="16">
         <v>4.73</v>
       </c>
-      <c r="T3" s="23">
-        <v>425.5</v>
+      <c r="T3" s="17">
+        <v>399.58</v>
       </c>
     </row>
     <row r="4">
@@ -4230,7 +4230,7 @@
       <c r="C4" t="str">
         <v>600418</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="38" t="str">
         <v>净卖: -8419.55万</v>
       </c>
       <c r="E4">
@@ -4245,7 +4245,7 @@
       <c r="H4">
         <v>-0.78</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="31">
         <v>-6.97</v>
       </c>
       <c r="J4" s="34">
@@ -4254,32 +4254,32 @@
       <c r="K4" s="35">
         <v>-7.89</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="30">
         <v>-7.79</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="39">
         <v>1.42</v>
       </c>
-      <c r="N4" s="39">
+      <c r="N4" s="32">
         <v>3.29</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="27">
         <v>10.45</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="33">
         <v>15.53</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q4" s="28">
         <v>12.95</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="36">
         <v>13.61</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="29">
         <v>11.08</v>
       </c>
-      <c r="T4" s="33">
-        <v>28.79</v>
+      <c r="T4" s="37">
+        <v>26.21</v>
       </c>
     </row>
     <row r="5">
@@ -4292,7 +4292,7 @@
       <c r="C5" t="str">
         <v>002856</v>
       </c>
-      <c r="D5" s="48" t="str">
+      <c r="D5" s="49" t="str">
         <v>净买: 382.36万</v>
       </c>
       <c r="E5">
@@ -4307,7 +4307,7 @@
       <c r="H5">
         <v>0.25</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="45">
         <v>-10</v>
       </c>
       <c r="J5" s="50">
@@ -4316,31 +4316,31 @@
       <c r="K5" s="52">
         <v>-1.82</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="46">
         <v>-10.66</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="51">
         <v>-12.81</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="40">
         <v>-10.33</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="47">
         <v>-9.92</v>
       </c>
       <c r="P5" s="42">
         <v>-11.24</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="43">
         <v>-10.25</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="48">
         <v>-11.07</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="41">
         <v>-12.73</v>
       </c>
-      <c r="T5" s="43">
+      <c r="T5" s="44">
         <v>8.43</v>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       <c r="C6" t="str">
         <v>001331</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="56" t="str">
         <v>净买: 966.34万</v>
       </c>
       <c r="E6">
@@ -4369,41 +4369,41 @@
       <c r="H6">
         <v>10.01</v>
       </c>
-      <c r="I6" s="55">
+      <c r="I6" s="64">
         <v>0</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="54">
         <v>-9.55</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="57">
         <v>-18.58</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="61">
         <v>-22.16</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="62">
         <v>-22.81</v>
       </c>
-      <c r="N6" s="59">
+      <c r="N6" s="58">
         <v>-22.42</v>
       </c>
-      <c r="O6" s="53">
+      <c r="O6" s="55">
         <v>-22.29</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="63">
         <v>-22.03</v>
       </c>
-      <c r="Q6" s="61">
+      <c r="Q6" s="65">
         <v>-18.52</v>
       </c>
-      <c r="R6" s="57">
+      <c r="R6" s="59">
         <v>-16.83</v>
       </c>
-      <c r="S6" s="54">
+      <c r="S6" s="53">
         <v>-16.76</v>
       </c>
-      <c r="T6" s="62">
-        <v>189.67</v>
+      <c r="T6" s="60">
+        <v>192.66</v>
       </c>
     </row>
     <row r="7">
@@ -4416,7 +4416,7 @@
       <c r="C7" t="str">
         <v>605169</v>
       </c>
-      <c r="D7" s="75" t="str">
+      <c r="D7" s="67" t="str">
         <v>净卖: -1118.05万</v>
       </c>
       <c r="E7">
@@ -4431,41 +4431,41 @@
       <c r="H7">
         <v>-4.72</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="77">
         <v>15.46</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="71">
         <v>12.98</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="72">
         <v>2.95</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="75">
         <v>-4.72</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="73">
         <v>-3.13</v>
       </c>
       <c r="N7" s="68">
         <v>-5.78</v>
       </c>
-      <c r="O7" s="73">
+      <c r="O7" s="69">
         <v>-5.01</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="78">
         <v>-6.43</v>
       </c>
-      <c r="Q7" s="74">
+      <c r="Q7" s="66">
         <v>-10.5</v>
       </c>
-      <c r="R7" s="69">
+      <c r="R7" s="70">
         <v>-9.79</v>
       </c>
-      <c r="S7" s="76">
+      <c r="S7" s="74">
         <v>-11.15</v>
       </c>
-      <c r="T7" s="70">
-        <v>-24.01</v>
+      <c r="T7" s="76">
+        <v>-25.31</v>
       </c>
     </row>
     <row r="8">
@@ -4478,7 +4478,7 @@
       <c r="C8" t="str">
         <v>836699</v>
       </c>
-      <c r="D8" s="91" t="str">
+      <c r="D8" s="79" t="str">
         <v>净卖: -801.39万</v>
       </c>
       <c r="E8">
@@ -4493,40 +4493,40 @@
       <c r="H8">
         <v>1.68</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="82">
         <v>27.86</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="85">
         <v>25.31</v>
       </c>
-      <c r="K8" s="84">
+      <c r="K8" s="86">
         <v>20.9</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="83">
         <v>14.59</v>
       </c>
-      <c r="M8" s="85">
+      <c r="M8" s="84">
         <v>31.58</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="90">
         <v>29.44</v>
       </c>
-      <c r="O8" s="90">
+      <c r="O8" s="91">
         <v>22.64</v>
       </c>
-      <c r="P8" s="86">
+      <c r="P8" s="87">
         <v>24.9</v>
       </c>
-      <c r="Q8" s="81">
+      <c r="Q8" s="88">
         <v>20.99</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="80">
         <v>18.14</v>
       </c>
-      <c r="S8" s="82">
+      <c r="S8" s="81">
         <v>36.74</v>
       </c>
-      <c r="T8" s="83">
+      <c r="T8" s="89">
         <v>30.08</v>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       <c r="C9" t="str">
         <v>301632</v>
       </c>
-      <c r="D9" s="102" t="str">
+      <c r="D9" s="93" t="str">
         <v>净买: 2340.61万</v>
       </c>
       <c r="E9">
@@ -4555,41 +4555,41 @@
       <c r="H9">
         <v>2.77</v>
       </c>
-      <c r="I9" s="103">
+      <c r="I9" s="100">
         <v>-13.93</v>
       </c>
       <c r="J9" s="94">
         <v>-17.96</v>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="101">
         <v>-18.95</v>
       </c>
-      <c r="L9" s="104">
+      <c r="L9" s="95">
         <v>-17</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="99">
         <v>-21.23</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="103">
         <v>-26.34</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="96">
         <v>-26.39</v>
       </c>
-      <c r="P9" s="99">
+      <c r="P9" s="97">
         <v>-25.82</v>
       </c>
-      <c r="Q9" s="100">
+      <c r="Q9" s="98">
         <v>-28.19</v>
       </c>
-      <c r="R9" s="96">
+      <c r="R9" s="104">
         <v>-30.97</v>
       </c>
-      <c r="S9" s="101">
+      <c r="S9" s="102">
         <v>-30.82</v>
       </c>
-      <c r="T9" s="93">
-        <v>-54.75</v>
+      <c r="T9" s="92">
+        <v>-55.63</v>
       </c>
     </row>
     <row r="10">
@@ -4602,7 +4602,7 @@
       <c r="C10" t="str">
         <v>300948</v>
       </c>
-      <c r="D10" s="115" t="str">
+      <c r="D10" s="106" t="str">
         <v>净卖: -709.60万</v>
       </c>
       <c r="E10">
@@ -4617,41 +4617,41 @@
       <c r="H10">
         <v>2.78</v>
       </c>
-      <c r="I10" s="116">
+      <c r="I10" s="113">
         <v>16.75</v>
       </c>
-      <c r="J10" s="110">
+      <c r="J10" s="109">
         <v>1.59</v>
       </c>
-      <c r="K10" s="107">
+      <c r="K10" s="114">
         <v>0.16</v>
       </c>
-      <c r="L10" s="117">
+      <c r="L10" s="107">
         <v>-2.23</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="108">
         <v>5.35</v>
       </c>
-      <c r="N10" s="108">
+      <c r="N10" s="117">
         <v>8.32</v>
       </c>
-      <c r="O10" s="112">
+      <c r="O10" s="115">
         <v>9.38</v>
       </c>
-      <c r="P10" s="113">
+      <c r="P10" s="110">
         <v>10.44</v>
       </c>
-      <c r="Q10" s="105">
+      <c r="Q10" s="111">
         <v>8.64</v>
       </c>
-      <c r="R10" s="114">
+      <c r="R10" s="112">
         <v>4.13</v>
       </c>
-      <c r="S10" s="109">
+      <c r="S10" s="116">
         <v>3.34</v>
       </c>
-      <c r="T10" s="106">
-        <v>6.36</v>
+      <c r="T10" s="105">
+        <v>4.19</v>
       </c>
     </row>
     <row r="11">
@@ -4664,7 +4664,7 @@
       <c r="C11" t="str">
         <v>000069</v>
       </c>
-      <c r="D11" s="118" t="str">
+      <c r="D11" s="124" t="str">
         <v>净买: 3152.70万</v>
       </c>
       <c r="E11">
@@ -4679,41 +4679,41 @@
       <c r="H11">
         <v>1.88</v>
       </c>
-      <c r="I11" s="128">
+      <c r="I11" s="125">
         <v>8.12</v>
       </c>
-      <c r="J11" s="119">
+      <c r="J11" s="128">
         <v>3.69</v>
       </c>
-      <c r="K11" s="120">
+      <c r="K11" s="129">
         <v>4.06</v>
       </c>
-      <c r="L11" s="121">
+      <c r="L11" s="118">
         <v>2.95</v>
       </c>
-      <c r="M11" s="124">
+      <c r="M11" s="126">
         <v>4.8</v>
       </c>
-      <c r="N11" s="129">
+      <c r="N11" s="119">
         <v>0.37</v>
       </c>
-      <c r="O11" s="125">
+      <c r="O11" s="127">
         <v>-2.95</v>
       </c>
-      <c r="P11" s="126">
+      <c r="P11" s="120">
         <v>0</v>
       </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="121">
         <v>-1.11</v>
       </c>
-      <c r="R11" s="130">
+      <c r="R11" s="122">
         <v>-1.85</v>
       </c>
-      <c r="S11" s="123">
+      <c r="S11" s="130">
         <v>0</v>
       </c>
-      <c r="T11" s="127">
-        <v>-19.56</v>
+      <c r="T11" s="123">
+        <v>-19.93</v>
       </c>
     </row>
     <row r="12">
@@ -4726,7 +4726,7 @@
       <c r="C12" t="str">
         <v>002242</v>
       </c>
-      <c r="D12" s="135" t="str">
+      <c r="D12" s="136" t="str">
         <v>净卖: -1077.90万</v>
       </c>
       <c r="E12">
@@ -4741,41 +4741,41 @@
       <c r="H12">
         <v>10.04</v>
       </c>
-      <c r="I12" s="139">
+      <c r="I12" s="142">
         <v>0</v>
       </c>
-      <c r="J12" s="142">
+      <c r="J12" s="137">
         <v>-4.93</v>
       </c>
-      <c r="K12" s="136">
+      <c r="K12" s="143">
         <v>-3.04</v>
       </c>
-      <c r="L12" s="143">
+      <c r="L12" s="138">
         <v>-11.42</v>
       </c>
-      <c r="M12" s="132">
+      <c r="M12" s="131">
         <v>-11.83</v>
       </c>
-      <c r="N12" s="140">
+      <c r="N12" s="132">
         <v>-15.61</v>
       </c>
-      <c r="O12" s="137">
+      <c r="O12" s="139">
         <v>-15.12</v>
       </c>
-      <c r="P12" s="138">
+      <c r="P12" s="133">
         <v>-14.71</v>
       </c>
-      <c r="Q12" s="133">
+      <c r="Q12" s="140">
         <v>-15.37</v>
       </c>
-      <c r="R12" s="141">
+      <c r="R12" s="134">
         <v>-14.13</v>
       </c>
-      <c r="S12" s="131">
+      <c r="S12" s="135">
         <v>-14.13</v>
       </c>
-      <c r="T12" s="134">
-        <v>-8.38</v>
+      <c r="T12" s="141">
+        <v>-11.18</v>
       </c>
     </row>
     <row r="13">
@@ -4788,7 +4788,7 @@
       <c r="C13" t="str">
         <v>603877</v>
       </c>
-      <c r="D13" s="153" t="str">
+      <c r="D13" s="145" t="str">
         <v>净卖: -596.03万</v>
       </c>
       <c r="E13">
@@ -4803,41 +4803,41 @@
       <c r="H13">
         <v>3.85</v>
       </c>
-      <c r="I13" s="147">
+      <c r="I13" s="148">
         <v>5.94</v>
       </c>
-      <c r="J13" s="154">
+      <c r="J13" s="149">
         <v>0</v>
       </c>
-      <c r="K13" s="144">
+      <c r="K13" s="150">
         <v>-6.18</v>
       </c>
-      <c r="L13" s="155">
+      <c r="L13" s="153">
         <v>-4.29</v>
       </c>
-      <c r="M13" s="152">
+      <c r="M13" s="151">
         <v>-4.94</v>
       </c>
-      <c r="N13" s="156">
+      <c r="N13" s="146">
         <v>-5</v>
       </c>
-      <c r="O13" s="145">
+      <c r="O13" s="144">
         <v>-7.41</v>
       </c>
-      <c r="P13" s="148">
+      <c r="P13" s="154">
         <v>-3.76</v>
       </c>
-      <c r="Q13" s="149">
+      <c r="Q13" s="155">
         <v>-4.12</v>
       </c>
-      <c r="R13" s="150">
+      <c r="R13" s="156">
         <v>-4.24</v>
       </c>
-      <c r="S13" s="146">
+      <c r="S13" s="147">
         <v>-5.88</v>
       </c>
-      <c r="T13" s="151">
-        <v>-15.41</v>
+      <c r="T13" s="152">
+        <v>-15.59</v>
       </c>
     </row>
     <row r="14">
@@ -4850,7 +4850,7 @@
       <c r="C14" t="str">
         <v>603216</v>
       </c>
-      <c r="D14" s="159" t="str">
+      <c r="D14" s="164" t="str">
         <v>净买: 462.51万</v>
       </c>
       <c r="E14">
@@ -4865,13 +4865,13 @@
       <c r="H14">
         <v>-6.54</v>
       </c>
-      <c r="I14" s="160">
+      <c r="I14" s="165">
         <v>-3.72</v>
       </c>
-      <c r="J14" s="167">
+      <c r="J14" s="166">
         <v>-9.38</v>
       </c>
-      <c r="K14" s="161">
+      <c r="K14" s="168">
         <v>-2.23</v>
       </c>
       <c r="L14" s="169">
@@ -4880,26 +4880,26 @@
       <c r="M14" s="162">
         <v>-0.51</v>
       </c>
-      <c r="N14" s="163">
+      <c r="N14" s="167">
         <v>9.31</v>
       </c>
-      <c r="O14" s="157">
+      <c r="O14" s="163">
         <v>5.63</v>
       </c>
-      <c r="P14" s="168">
+      <c r="P14" s="158">
         <v>5.63</v>
       </c>
-      <c r="Q14" s="158">
+      <c r="Q14" s="157">
         <v>11.51</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="159">
         <v>11.89</v>
       </c>
-      <c r="S14" s="165">
+      <c r="S14" s="160">
         <v>2.92</v>
       </c>
-      <c r="T14" s="166">
-        <v>-4.67</v>
+      <c r="T14" s="161">
+        <v>-6.39</v>
       </c>
     </row>
     <row r="15">
@@ -4912,7 +4912,7 @@
       <c r="C15" t="str">
         <v>002589</v>
       </c>
-      <c r="D15" s="174" t="str">
+      <c r="D15" s="179" t="str">
         <v>净买: 1428.73万</v>
       </c>
       <c r="E15">
@@ -4927,41 +4927,41 @@
       <c r="H15">
         <v>-5.54</v>
       </c>
-      <c r="I15" s="182">
+      <c r="I15" s="180">
         <v>-4.74</v>
       </c>
-      <c r="J15" s="179">
+      <c r="J15" s="181">
         <v>-11.96</v>
       </c>
-      <c r="K15" s="175">
+      <c r="K15" s="178">
         <v>-19.86</v>
       </c>
-      <c r="L15" s="180">
+      <c r="L15" s="171">
         <v>-20.77</v>
       </c>
-      <c r="M15" s="181">
+      <c r="M15" s="174">
         <v>-18.96</v>
       </c>
-      <c r="N15" s="176">
+      <c r="N15" s="175">
         <v>-23.25</v>
       </c>
-      <c r="O15" s="170">
+      <c r="O15" s="172">
         <v>-23.7</v>
       </c>
-      <c r="P15" s="173">
+      <c r="P15" s="182">
         <v>-20.77</v>
       </c>
-      <c r="Q15" s="171">
+      <c r="Q15" s="176">
         <v>-19.86</v>
       </c>
-      <c r="R15" s="172">
+      <c r="R15" s="177">
         <v>-20.32</v>
       </c>
-      <c r="S15" s="177">
+      <c r="S15" s="173">
         <v>-22.8</v>
       </c>
-      <c r="T15" s="178">
-        <v>-27.54</v>
+      <c r="T15" s="170">
+        <v>-27.31</v>
       </c>
     </row>
     <row r="16">
@@ -4974,7 +4974,7 @@
       <c r="C16" t="str">
         <v>605255</v>
       </c>
-      <c r="D16" s="188" t="str">
+      <c r="D16" s="184" t="str">
         <v>净卖: -745.64万</v>
       </c>
       <c r="E16">
@@ -4992,38 +4992,38 @@
       <c r="I16" s="189">
         <v>0</v>
       </c>
-      <c r="J16" s="183">
+      <c r="J16" s="187">
         <v>-10</v>
       </c>
-      <c r="K16" s="191">
+      <c r="K16" s="190">
         <v>-1</v>
       </c>
-      <c r="L16" s="184">
+      <c r="L16" s="188">
         <v>-10.9</v>
       </c>
-      <c r="M16" s="190">
+      <c r="M16" s="185">
         <v>-17.03</v>
       </c>
-      <c r="N16" s="192">
+      <c r="N16" s="191">
         <v>-11.34</v>
       </c>
-      <c r="O16" s="185">
+      <c r="O16" s="186">
         <v>-8.27</v>
       </c>
-      <c r="P16" s="193">
+      <c r="P16" s="194">
         <v>-9.76</v>
       </c>
-      <c r="Q16" s="194">
+      <c r="Q16" s="195">
         <v>-11.21</v>
       </c>
-      <c r="R16" s="186">
+      <c r="R16" s="192">
         <v>-12.68</v>
       </c>
-      <c r="S16" s="187">
+      <c r="S16" s="183">
         <v>-21.41</v>
       </c>
-      <c r="T16" s="195">
-        <v>-44.69</v>
+      <c r="T16" s="193">
+        <v>-48.02</v>
       </c>
     </row>
     <row r="17">
@@ -5036,7 +5036,7 @@
       <c r="C17" t="str">
         <v>601139</v>
       </c>
-      <c r="D17" s="203" t="str">
+      <c r="D17" s="205" t="str">
         <v>净卖: -3779.77万</v>
       </c>
       <c r="E17">
@@ -5051,41 +5051,41 @@
       <c r="H17">
         <v>1.68</v>
       </c>
-      <c r="I17" s="208">
+      <c r="I17" s="199">
         <v>8.25</v>
       </c>
-      <c r="J17" s="204">
+      <c r="J17" s="206">
         <v>0.41</v>
       </c>
-      <c r="K17" s="205">
+      <c r="K17" s="200">
         <v>-3.58</v>
       </c>
-      <c r="L17" s="196">
+      <c r="L17" s="207">
         <v>-3.03</v>
       </c>
-      <c r="M17" s="206">
+      <c r="M17" s="201">
         <v>-0.55</v>
       </c>
-      <c r="N17" s="200">
+      <c r="N17" s="202">
         <v>-1.79</v>
       </c>
-      <c r="O17" s="201">
+      <c r="O17" s="208">
         <v>-0.41</v>
       </c>
-      <c r="P17" s="197">
+      <c r="P17" s="203">
         <v>7.7</v>
       </c>
-      <c r="Q17" s="198">
+      <c r="Q17" s="196">
         <v>5.23</v>
       </c>
-      <c r="R17" s="199">
+      <c r="R17" s="204">
         <v>3.03</v>
       </c>
-      <c r="S17" s="207">
+      <c r="S17" s="197">
         <v>0</v>
       </c>
-      <c r="T17" s="202">
-        <v>-3.58</v>
+      <c r="T17" s="198">
+        <v>-2.61</v>
       </c>
     </row>
     <row r="18">
@@ -5147,40 +5147,40 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="209">
+      <c r="I19" s="212">
         <v>43.75</v>
       </c>
-      <c r="J19" s="214">
+      <c r="J19" s="216">
         <v>31.25</v>
       </c>
-      <c r="K19" s="215">
+      <c r="K19" s="217">
         <v>25</v>
       </c>
-      <c r="L19" s="216">
+      <c r="L19" s="219">
         <v>18.75</v>
       </c>
-      <c r="M19" s="210">
+      <c r="M19" s="213">
         <v>31.25</v>
       </c>
-      <c r="N19" s="217">
+      <c r="N19" s="220">
         <v>37.5</v>
       </c>
-      <c r="O19" s="211">
+      <c r="O19" s="209">
         <v>31.25</v>
       </c>
-      <c r="P19" s="212">
+      <c r="P19" s="214">
         <v>37.5</v>
       </c>
       <c r="Q19" s="218">
         <v>37.5</v>
       </c>
-      <c r="R19" s="213">
+      <c r="R19" s="210">
         <v>37.5</v>
       </c>
-      <c r="S19" s="219">
+      <c r="S19" s="211">
         <v>31.25</v>
       </c>
-      <c r="T19" s="220">
+      <c r="T19" s="215">
         <v>43.75</v>
       </c>
     </row>
@@ -5195,41 +5195,41 @@
       <c r="F20" t="str"/>
       <c r="G20" t="str"/>
       <c r="H20" t="str"/>
-      <c r="I20" s="222">
+      <c r="I20" s="232">
         <v>3.11</v>
       </c>
-      <c r="J20" s="223">
+      <c r="J20" s="228">
         <v>-2.73</v>
       </c>
-      <c r="K20" s="224">
+      <c r="K20" s="221">
         <v>-4.91</v>
       </c>
-      <c r="L20" s="230">
+      <c r="L20" s="229">
         <v>-7.8</v>
       </c>
-      <c r="M20" s="232">
+      <c r="M20" s="223">
         <v>-5.55</v>
       </c>
-      <c r="N20" s="227">
+      <c r="N20" s="226">
         <v>-5.78</v>
       </c>
-      <c r="O20" s="225">
+      <c r="O20" s="222">
         <v>-6.29</v>
       </c>
-      <c r="P20" s="231">
+      <c r="P20" s="230">
         <v>-4.87</v>
       </c>
-      <c r="Q20" s="221">
+      <c r="Q20" s="231">
         <v>-5.25</v>
       </c>
-      <c r="R20" s="228">
+      <c r="R20" s="224">
         <v>-5.94</v>
       </c>
-      <c r="S20" s="226">
+      <c r="S20" s="225">
         <v>-6.59</v>
       </c>
-      <c r="T20" s="229">
-        <v>36.69</v>
+      <c r="T20" s="227">
+        <v>34.72</v>
       </c>
     </row>
   </sheetData>
